--- a/src/Excelsior.Tests/NaughtyStringsTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/NaughtyStringsTests.Test.verified.xlsx
@@ -51,6 +51,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -59,6 +60,11 @@
           <t xml:space="preserve">Value</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Html</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -66,6 +72,13 @@
           <t xml:space="preserve">undefined</t>
         </is>
       </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">undefined</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -73,6 +86,13 @@
           <t xml:space="preserve">undef</t>
         </is>
       </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">undef</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -80,6 +100,13 @@
           <t xml:space="preserve">null</t>
         </is>
       </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">null</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -87,6 +114,13 @@
           <t xml:space="preserve">NULL</t>
         </is>
       </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">NULL</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -94,6 +128,13 @@
           <t xml:space="preserve">(null)</t>
         </is>
       </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">(null)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -101,6 +142,13 @@
           <t xml:space="preserve">nil</t>
         </is>
       </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">nil</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -108,6 +156,13 @@
           <t xml:space="preserve">NIL</t>
         </is>
       </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">NIL</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -115,6 +170,13 @@
           <t xml:space="preserve">true</t>
         </is>
       </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">true</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -122,6 +184,13 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">false</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -129,6 +198,13 @@
           <t xml:space="preserve">True</t>
         </is>
       </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">True</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -136,6 +212,13 @@
           <t xml:space="preserve">False</t>
         </is>
       </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">False</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -143,6 +226,13 @@
           <t xml:space="preserve">TRUE</t>
         </is>
       </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">TRUE</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -150,6 +240,13 @@
           <t xml:space="preserve">FALSE</t>
         </is>
       </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FALSE</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -157,6 +254,13 @@
           <t xml:space="preserve">None</t>
         </is>
       </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">None</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -164,6 +268,13 @@
           <t xml:space="preserve">hasOwnProperty</t>
         </is>
       </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">hasOwnProperty</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -171,6 +282,13 @@
           <t xml:space="preserve">then</t>
         </is>
       </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">then</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -178,6 +296,13 @@
           <t xml:space="preserve">constructor</t>
         </is>
       </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">constructor</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -185,6 +310,13 @@
           <t xml:space="preserve">\</t>
         </is>
       </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">\</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -192,6 +324,13 @@
           <t xml:space="preserve">\\</t>
         </is>
       </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">\\</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -199,6 +338,13 @@
           <t xml:space="preserve">0</t>
         </is>
       </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -206,6 +352,13 @@
           <t xml:space="preserve">1</t>
         </is>
       </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -213,6 +366,13 @@
           <t xml:space="preserve">1.00</t>
         </is>
       </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1.00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -220,6 +380,13 @@
           <t xml:space="preserve">$1.00</t>
         </is>
       </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">$1.00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -227,6 +394,13 @@
           <t xml:space="preserve">1/2</t>
         </is>
       </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/2</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -234,6 +408,13 @@
           <t xml:space="preserve">1E2</t>
         </is>
       </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1E2</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -241,6 +422,13 @@
           <t xml:space="preserve">1E02</t>
         </is>
       </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1E02</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -248,6 +436,13 @@
           <t xml:space="preserve">1E+02</t>
         </is>
       </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1E+02</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -255,6 +450,13 @@
           <t xml:space="preserve">-1</t>
         </is>
       </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -262,6 +464,13 @@
           <t xml:space="preserve">-1.00</t>
         </is>
       </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-1.00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -269,6 +478,13 @@
           <t xml:space="preserve">-$1.00</t>
         </is>
       </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-$1.00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -276,6 +492,13 @@
           <t xml:space="preserve">-1/2</t>
         </is>
       </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-1/2</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -283,6 +506,13 @@
           <t xml:space="preserve">-1E2</t>
         </is>
       </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-1E2</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -290,6 +520,13 @@
           <t xml:space="preserve">-1E02</t>
         </is>
       </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-1E02</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -297,6 +534,13 @@
           <t xml:space="preserve">-1E+02</t>
         </is>
       </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-1E+02</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -304,6 +548,13 @@
           <t xml:space="preserve">1/0</t>
         </is>
       </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -311,6 +562,13 @@
           <t xml:space="preserve">0/0</t>
         </is>
       </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0/0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -318,6 +576,13 @@
           <t xml:space="preserve">-2147483648/-1</t>
         </is>
       </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-2147483648/-1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -325,6 +590,13 @@
           <t xml:space="preserve">-9223372036854775808/-1</t>
         </is>
       </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-9223372036854775808/-1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -332,6 +604,13 @@
           <t xml:space="preserve">-0</t>
         </is>
       </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -339,6 +618,13 @@
           <t xml:space="preserve">-0.0</t>
         </is>
       </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-0.0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -346,6 +632,13 @@
           <t xml:space="preserve">+0</t>
         </is>
       </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">+0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -353,6 +646,13 @@
           <t xml:space="preserve">+0.0</t>
         </is>
       </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">+0.0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -360,6 +660,13 @@
           <t xml:space="preserve">0.00</t>
         </is>
       </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0.00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -367,6 +674,13 @@
           <t xml:space="preserve">0..0</t>
         </is>
       </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0..0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -374,6 +688,13 @@
           <t xml:space="preserve">.</t>
         </is>
       </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">.</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -381,6 +702,13 @@
           <t xml:space="preserve">0.0.0</t>
         </is>
       </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0.0.0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -388,6 +716,13 @@
           <t xml:space="preserve">0,00</t>
         </is>
       </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0,00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -395,6 +730,13 @@
           <t xml:space="preserve">0,,0</t>
         </is>
       </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0,,0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -402,6 +744,13 @@
           <t xml:space="preserve">,</t>
         </is>
       </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">,</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -409,6 +758,13 @@
           <t xml:space="preserve">0,0,0</t>
         </is>
       </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0,0,0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -416,6 +772,13 @@
           <t xml:space="preserve">0.0/0</t>
         </is>
       </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0.0/0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -423,6 +786,13 @@
           <t xml:space="preserve">1.0/0.0</t>
         </is>
       </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1.0/0.0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -430,6 +800,13 @@
           <t xml:space="preserve">0.0/0.0</t>
         </is>
       </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0.0/0.0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -437,6 +814,13 @@
           <t xml:space="preserve">1,0/0,0</t>
         </is>
       </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1,0/0,0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -444,6 +828,13 @@
           <t xml:space="preserve">0,0/0,0</t>
         </is>
       </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0,0/0,0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -451,6 +842,13 @@
           <t xml:space="preserve">--1</t>
         </is>
       </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">--1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -458,6 +856,13 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -465,6 +870,13 @@
           <t xml:space="preserve">-.</t>
         </is>
       </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-.</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -472,6 +884,13 @@
           <t xml:space="preserve">-,</t>
         </is>
       </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-,</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -479,6 +898,13 @@
           <t xml:space="preserve">999999999999999999999999999999999999999999999999999999999999999999999999999999999999999999999999</t>
         </is>
       </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">999999999999999999999999999999999999999999999999999999999999999999999999999999999999999999999999</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -486,6 +912,13 @@
           <t xml:space="preserve">NaN</t>
         </is>
       </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">NaN</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -493,6 +926,13 @@
           <t xml:space="preserve">Infinity</t>
         </is>
       </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Infinity</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -500,6 +940,13 @@
           <t xml:space="preserve">-Infinity</t>
         </is>
       </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-Infinity</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -507,6 +954,13 @@
           <t xml:space="preserve">INF</t>
         </is>
       </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">INF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -514,6 +968,13 @@
           <t xml:space="preserve">1#INF</t>
         </is>
       </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1#INF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -521,6 +982,13 @@
           <t xml:space="preserve">-1#IND</t>
         </is>
       </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-1#IND</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -528,6 +996,13 @@
           <t xml:space="preserve">1#QNAN</t>
         </is>
       </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1#QNAN</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -535,6 +1010,13 @@
           <t xml:space="preserve">1#SNAN</t>
         </is>
       </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1#SNAN</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -542,6 +1024,13 @@
           <t xml:space="preserve">1#IND</t>
         </is>
       </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1#IND</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -549,6 +1038,13 @@
           <t xml:space="preserve">0x0</t>
         </is>
       </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0x0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -556,6 +1052,13 @@
           <t xml:space="preserve">0xffffffff</t>
         </is>
       </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0xffffffff</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -563,6 +1066,13 @@
           <t xml:space="preserve">0xffffffffffffffff</t>
         </is>
       </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0xffffffffffffffff</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -570,6 +1080,13 @@
           <t xml:space="preserve">0xabad1dea</t>
         </is>
       </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0xabad1dea</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -577,6 +1094,13 @@
           <t xml:space="preserve">123456789012345678901234567890123456789</t>
         </is>
       </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">123456789012345678901234567890123456789</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -584,6 +1108,13 @@
           <t xml:space="preserve">1,000.00</t>
         </is>
       </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1,000.00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -591,6 +1122,13 @@
           <t xml:space="preserve">1 000.00</t>
         </is>
       </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1 000.00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -598,6 +1136,13 @@
           <t xml:space="preserve">1'000.00</t>
         </is>
       </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1'000.00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -605,6 +1150,13 @@
           <t xml:space="preserve">1,000,000.00</t>
         </is>
       </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1,000,000.00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -612,6 +1164,13 @@
           <t xml:space="preserve">1 000 000.00</t>
         </is>
       </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1 000 000.00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -619,6 +1178,13 @@
           <t xml:space="preserve">1'000'000.00</t>
         </is>
       </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1'000'000.00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -626,6 +1192,13 @@
           <t xml:space="preserve">1.000,00</t>
         </is>
       </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1.000,00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -633,6 +1206,13 @@
           <t xml:space="preserve">1 000,00</t>
         </is>
       </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1 000,00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -640,6 +1220,13 @@
           <t xml:space="preserve">1'000,00</t>
         </is>
       </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1'000,00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -647,6 +1234,13 @@
           <t xml:space="preserve">1.000.000,00</t>
         </is>
       </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1.000.000,00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -654,6 +1248,13 @@
           <t xml:space="preserve">1 000 000,00</t>
         </is>
       </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1 000 000,00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -661,6 +1262,13 @@
           <t xml:space="preserve">1'000'000,00</t>
         </is>
       </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1'000'000,00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -668,6 +1276,13 @@
           <t xml:space="preserve">01000</t>
         </is>
       </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">01000</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -675,6 +1290,13 @@
           <t xml:space="preserve">08</t>
         </is>
       </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">08</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -682,6 +1304,13 @@
           <t xml:space="preserve">09</t>
         </is>
       </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">09</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -689,6 +1318,13 @@
           <t xml:space="preserve">2.2250738585072011e-308</t>
         </is>
       </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2.2250738585072011e-308</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -696,6 +1332,13 @@
           <t xml:space="preserve">,./;'[]\-=</t>
         </is>
       </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">,./;'[]\-=</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -703,6 +1346,13 @@
           <t xml:space="preserve">&lt;&gt;?:"{}|_+</t>
         </is>
       </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">&lt;&gt;?:"{}|_+</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -710,6 +1360,13 @@
           <t xml:space="preserve">!@#$%^&amp;*()`~</t>
         </is>
       </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">!@#$%^&amp;*()`~</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -717,6 +1374,13 @@
           <t xml:space="preserve"></t>
         </is>
       </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"></t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -724,6 +1388,13 @@
           <t xml:space="preserve"></t>
         </is>
       </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"></t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -731,6 +1402,13 @@
           <t xml:space="preserve">\t \u0085             ​\u2028\u2029</t>
         </is>
       </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">\t \u0085 ​\u2028\u2029</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -738,6 +1416,13 @@
           <t xml:space="preserve">­؀؁؂؃؄؅؜۝܏᠎​‌‍‎‏‪‫‬‭‮⁠⁡⁢⁣⁤⁦⁧⁨⁩⁪⁫⁬⁭⁮⁯﻿￹￺￻𑂽𛲠𛲡𛲢𛲣𝅳𝅴𝅵𝅶𝅷𝅸𝅹𝅺󠀁󠀠󠀡󠀢󠀣󠀤󠀥󠀦󠀧󠀨󠀩󠀪󠀫󠀬󠀭󠀮󠀯󠀰󠀱󠀲󠀳󠀴󠀵󠀶󠀷󠀸󠀹󠀺󠀻󠀼󠀽󠀾󠀿󠁀󠁁󠁂󠁃󠁄󠁅󠁆󠁇󠁈󠁉󠁊󠁋󠁌󠁍󠁎󠁏󠁐󠁑󠁒󠁓󠁔󠁕󠁖󠁗󠁘󠁙󠁚󠁛󠁜󠁝󠁞󠁟󠁠󠁡󠁢󠁣󠁤󠁥󠁦󠁧󠁨󠁩󠁪󠁫󠁬󠁭󠁮󠁯󠁰󠁱󠁲󠁳󠁴󠁵󠁶󠁷󠁸󠁹󠁺󠁻󠁼󠁽󠁾󠁿</t>
         </is>
       </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">­؀؁؂؃؄؅؜۝܏᠎​‌‍‎‏‪‫‬‭‮⁠⁡⁢⁣⁤⁦⁧⁨⁩⁪⁫⁬⁭⁮⁯﻿￹￺￻𑂽𛲠𛲡𛲢𛲣𝅳𝅴𝅵𝅶𝅷𝅸𝅹𝅺󠀁󠀠󠀡󠀢󠀣󠀤󠀥󠀦󠀧󠀨󠀩󠀪󠀫󠀬󠀭󠀮󠀯󠀰󠀱󠀲󠀳󠀴󠀵󠀶󠀷󠀸󠀹󠀺󠀻󠀼󠀽󠀾󠀿󠁀󠁁󠁂󠁃󠁄󠁅󠁆󠁇󠁈󠁉󠁊󠁋󠁌󠁍󠁎󠁏󠁐󠁑󠁒󠁓󠁔󠁕󠁖󠁗󠁘󠁙󠁚󠁛󠁜󠁝󠁞󠁟󠁠󠁡󠁢󠁣󠁤󠁥󠁦󠁧󠁨󠁩󠁪󠁫󠁬󠁭󠁮󠁯󠁰󠁱󠁲󠁳󠁴󠁵󠁶󠁷󠁸󠁹󠁺󠁻󠁼󠁽󠁾󠁿</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -745,6 +1430,13 @@
           <t xml:space="preserve">﻿</t>
         </is>
       </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">﻿</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -752,6 +1444,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -759,6 +1454,13 @@
           <t xml:space="preserve">Ω≈ç√∫˜µ≤≥÷</t>
         </is>
       </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Ω≈ç√∫˜µ≤≥÷</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -766,6 +1468,13 @@
           <t xml:space="preserve">åß∂ƒ©˙∆˚¬…æ</t>
         </is>
       </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">åß∂ƒ©˙∆˚¬…æ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -773,6 +1482,13 @@
           <t xml:space="preserve">œ∑´®†¥¨ˆøπ“‘</t>
         </is>
       </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">œ∑´®†¥¨ˆøπ“‘</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -780,6 +1496,13 @@
           <t xml:space="preserve">¡™£¢∞§¶•ªº–≠</t>
         </is>
       </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">¡™£¢∞§¶•ªº–≠</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -787,6 +1510,13 @@
           <t xml:space="preserve">¸˛Ç◊ı˜Â¯˘¿</t>
         </is>
       </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">¸˛Ç◊ı˜Â¯˘¿</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -794,6 +1524,13 @@
           <t xml:space="preserve">ÅÍÎÏ˝ÓÔÒÚÆ☃</t>
         </is>
       </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ÅÍÎÏ˝ÓÔÒÚÆ☃</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -801,6 +1538,13 @@
           <t xml:space="preserve">Œ„´‰ˇÁ¨ˆØ∏”’</t>
         </is>
       </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Œ„´‰ˇÁ¨ˆØ∏”’</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -808,6 +1552,13 @@
           <t xml:space="preserve">`⁄€‹›ﬁﬂ‡°·‚—±</t>
         </is>
       </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">`⁄€‹›ﬁﬂ‡°·‚—±</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -815,6 +1566,13 @@
           <t xml:space="preserve">⅛⅜⅝⅞</t>
         </is>
       </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">⅛⅜⅝⅞</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -822,6 +1580,13 @@
           <t xml:space="preserve">ЁЂЃЄЅІЇЈЉЊЋЌЍЎЏАБВГДЕЖЗИЙКЛМНОПРСТУФХЦЧШЩЪЫЬЭЮЯабвгдежзийклмнопрстуфхцчшщъыьэюя</t>
         </is>
       </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ЁЂЃЄЅІЇЈЉЊЋЌЍЎЏАБВГДЕЖЗИЙКЛМНОПРСТУФХЦЧШЩЪЫЬЭЮЯабвгдежзийклмнопрстуфхцчшщъыьэюя</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -829,6 +1594,13 @@
           <t xml:space="preserve">٠١٢٣٤٥٦٧٨٩</t>
         </is>
       </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">٠١٢٣٤٥٦٧٨٩</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -836,6 +1608,13 @@
           <t xml:space="preserve">⁰⁴⁵</t>
         </is>
       </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">⁰⁴⁵</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -843,6 +1622,13 @@
           <t xml:space="preserve">₀₁₂</t>
         </is>
       </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">₀₁₂</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -850,6 +1636,13 @@
           <t xml:space="preserve">⁰⁴⁵₀₁₂</t>
         </is>
       </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">⁰⁴⁵₀₁₂</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -857,6 +1650,13 @@
           <t xml:space="preserve">ด้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็ ด้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็ ด้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็</t>
         </is>
       </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ด้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็ ด้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็ ด้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็็้้้้้้้้็็็็็้้้้้็็็็</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -864,6 +1664,13 @@
           <t xml:space="preserve">'</t>
         </is>
       </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">'</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -871,6 +1678,13 @@
           <t xml:space="preserve">"</t>
         </is>
       </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -878,6 +1692,13 @@
           <t xml:space="preserve">''</t>
         </is>
       </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">''</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -885,6 +1706,13 @@
           <t xml:space="preserve">""</t>
         </is>
       </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">""</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -892,6 +1720,13 @@
           <t xml:space="preserve">'"'</t>
         </is>
       </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">'"'</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -899,6 +1734,13 @@
           <t xml:space="preserve">"''''"'"</t>
         </is>
       </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"''''"'"</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -906,6 +1748,13 @@
           <t xml:space="preserve">"'"'"''''"</t>
         </is>
       </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"'"'"''''"</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -913,6 +1762,9 @@
           <t xml:space="preserve">&lt;foo val=“bar” /&gt;</t>
         </is>
       </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -920,6 +1772,9 @@
           <t xml:space="preserve">&lt;foo val=“bar” /&gt;</t>
         </is>
       </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -927,6 +1782,9 @@
           <t xml:space="preserve">&lt;foo val=”bar“ /&gt;</t>
         </is>
       </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -934,6 +1792,9 @@
           <t xml:space="preserve">&lt;foo val=`bar' /&gt;</t>
         </is>
       </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -941,6 +1802,13 @@
           <t xml:space="preserve">田中さんにあげて下さい</t>
         </is>
       </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">田中さんにあげて下さい</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -948,6 +1816,13 @@
           <t xml:space="preserve">パーティーへ行かないか</t>
         </is>
       </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">パーティーへ行かないか</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -955,6 +1830,13 @@
           <t xml:space="preserve">和製漢語</t>
         </is>
       </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">和製漢語</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -962,6 +1844,13 @@
           <t xml:space="preserve">部落格</t>
         </is>
       </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">部落格</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -969,6 +1858,13 @@
           <t xml:space="preserve">사회과학원 어학연구소</t>
         </is>
       </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">사회과학원 어학연구소</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -976,6 +1872,13 @@
           <t xml:space="preserve">찦차를 타고 온 펲시맨과 쑛다리 똠방각하</t>
         </is>
       </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">찦차를 타고 온 펲시맨과 쑛다리 똠방각하</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -983,6 +1886,13 @@
           <t xml:space="preserve">社會科學院語學研究所</t>
         </is>
       </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">社會科學院語學研究所</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -990,6 +1900,13 @@
           <t xml:space="preserve">울란바토르</t>
         </is>
       </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">울란바토르</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -997,6 +1914,13 @@
           <t xml:space="preserve">𠜎𠜱𠝹𠱓𠱸𠲖𠳏</t>
         </is>
       </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">𠜎𠜱𠝹𠱓𠱸𠲖𠳏</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -1004,6 +1928,13 @@
           <t xml:space="preserve">𐐜 𐐔𐐇𐐝𐐀𐐡𐐇𐐓 𐐙𐐊𐐡𐐝𐐓/𐐝𐐇𐐗𐐊𐐤𐐔 𐐒𐐋𐐗 𐐒𐐌 𐐜 𐐡𐐀𐐖𐐇𐐤𐐓𐐝 𐐱𐑂 𐑄 𐐔𐐇𐐝𐐀𐐡𐐇𐐓 𐐏𐐆𐐅𐐤𐐆𐐚𐐊𐐡𐐝𐐆𐐓𐐆</t>
         </is>
       </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">𐐜 𐐔𐐇𐐝𐐀𐐡𐐇𐐓 𐐙𐐊𐐡𐐝𐐓/𐐝𐐇𐐗𐐊𐐤𐐔 𐐒𐐋𐐗 𐐒𐐌 𐐜 𐐡𐐀𐐖𐐇𐐤𐐓𐐝 𐐱𐑂 𐑄 𐐔𐐇𐐝𐐀𐐡𐐇𐐓 𐐏𐐆𐐅𐐤𐐆𐐚𐐊𐐡𐐝𐐆𐐓𐐆</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -1011,6 +1942,13 @@
           <t xml:space="preserve">表</t>
         </is>
       </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">表</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -1018,6 +1956,13 @@
           <t xml:space="preserve">ポ</t>
         </is>
       </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ポ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -1025,6 +1970,13 @@
           <t xml:space="preserve">あ</t>
         </is>
       </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">あ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -1032,6 +1984,13 @@
           <t xml:space="preserve">A</t>
         </is>
       </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">A</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -1039,6 +1998,13 @@
           <t xml:space="preserve">鷗</t>
         </is>
       </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">鷗</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -1046,6 +2012,13 @@
           <t xml:space="preserve">Œ</t>
         </is>
       </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Œ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -1053,6 +2026,13 @@
           <t xml:space="preserve">é</t>
         </is>
       </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">é</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -1060,6 +2040,13 @@
           <t xml:space="preserve">Ｂ</t>
         </is>
       </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Ｂ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -1067,6 +2054,13 @@
           <t xml:space="preserve">逍</t>
         </is>
       </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">逍</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -1074,6 +2068,13 @@
           <t xml:space="preserve">Ü</t>
         </is>
       </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Ü</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -1081,6 +2082,13 @@
           <t xml:space="preserve">ß</t>
         </is>
       </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ß</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -1088,6 +2096,13 @@
           <t xml:space="preserve">ª</t>
         </is>
       </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ª</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -1095,6 +2110,13 @@
           <t xml:space="preserve">ą</t>
         </is>
       </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ą</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -1102,6 +2124,13 @@
           <t xml:space="preserve">ñ</t>
         </is>
       </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ñ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -1109,6 +2138,13 @@
           <t xml:space="preserve">丂</t>
         </is>
       </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">丂</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -1116,6 +2152,13 @@
           <t xml:space="preserve">㐀</t>
         </is>
       </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">㐀</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -1123,6 +2166,13 @@
           <t xml:space="preserve">𠀀</t>
         </is>
       </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">𠀀</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -1130,6 +2180,13 @@
           <t xml:space="preserve">Ⱥ</t>
         </is>
       </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Ⱥ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -1137,6 +2194,13 @@
           <t xml:space="preserve">Ⱦ</t>
         </is>
       </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Ⱦ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -1144,6 +2208,13 @@
           <t xml:space="preserve">ヽ༼ຈل͜ຈ༽ﾉ ヽ༼ຈل͜ຈ༽ﾉ</t>
         </is>
       </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ヽ༼ຈل͜ຈ༽ﾉ ヽ༼ຈل͜ຈ༽ﾉ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -1151,6 +2222,13 @@
           <t xml:space="preserve">(｡◕ ∀ ◕｡)</t>
         </is>
       </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">(｡◕ ∀ ◕｡)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -1158,6 +2236,13 @@
           <t xml:space="preserve">｀ｨ(´∀｀∩</t>
         </is>
       </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">｀ｨ(´∀｀∩</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -1165,6 +2250,13 @@
           <t xml:space="preserve">__ﾛ(,_,*)</t>
         </is>
       </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">__ﾛ(,_,*)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -1172,6 +2264,13 @@
           <t xml:space="preserve">・(￣∀￣)・:*:</t>
         </is>
       </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">・(￣∀￣)・:*:</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -1179,6 +2278,13 @@
           <t xml:space="preserve">ﾟ･✿ヾ╲(｡◕‿◕｡)╱✿･ﾟ</t>
         </is>
       </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ﾟ･✿ヾ╲(｡◕‿◕｡)╱✿･ﾟ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -1186,6 +2292,13 @@
           <t xml:space="preserve">,。・:*:・゜’( ☻ ω ☻ )。・:*:・゜’</t>
         </is>
       </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">,。・:*:・゜’( ☻ ω ☻ )。・:*:・゜’</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -1193,6 +2306,13 @@
           <t xml:space="preserve">(╯°□°）╯︵ ┻━┻)</t>
         </is>
       </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">(╯°□°）╯︵ ┻━┻)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -1200,6 +2320,13 @@
           <t xml:space="preserve">(ﾉಥ益ಥ）ﾉ﻿ ┻━┻</t>
         </is>
       </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">(ﾉಥ益ಥ）ﾉ﻿ ┻━┻</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -1207,6 +2334,13 @@
           <t xml:space="preserve">┬─┬ノ( º _ ºノ)</t>
         </is>
       </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">┬─┬ノ( º _ ºノ)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -1214,6 +2348,13 @@
           <t xml:space="preserve">( ͡° ͜ʖ ͡°)</t>
         </is>
       </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">( ͡° ͜ʖ ͡°)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -1221,6 +2362,13 @@
           <t xml:space="preserve">¯\_(ツ)_/¯</t>
         </is>
       </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">¯\_(ツ)_/¯</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -1228,6 +2376,13 @@
           <t xml:space="preserve">😍</t>
         </is>
       </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">😍</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -1235,6 +2390,13 @@
           <t xml:space="preserve">👩🏽</t>
         </is>
       </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">👩🏽</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -1242,6 +2404,13 @@
           <t xml:space="preserve">👨‍🦰 👨🏿‍🦰 👨‍🦱 👨🏿‍🦱 🦹🏿‍♂️</t>
         </is>
       </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">👨‍🦰 👨🏿‍🦰 👨‍🦱 👨🏿‍🦱 🦹🏿‍♂️</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -1249,6 +2418,13 @@
           <t xml:space="preserve">👾 🙇 💁 🙅 🙆 🙋 🙎 🙍</t>
         </is>
       </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">👾 🙇 💁 🙅 🙆 🙋 🙎 🙍</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -1256,6 +2432,13 @@
           <t xml:space="preserve">🐵 🙈 🙉 🙊</t>
         </is>
       </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">🐵 🙈 🙉 🙊</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -1263,6 +2446,13 @@
           <t xml:space="preserve">❤️ 💔 💌 💕 💞 💓 💗 💖 💘 💝 💟 💜 💛 💚 💙</t>
         </is>
       </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">❤️ 💔 💌 💕 💞 💓 💗 💖 💘 💝 💟 💜 💛 💚 💙</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -1270,6 +2460,13 @@
           <t xml:space="preserve">✋🏿 💪🏿 👐🏿 🙌🏿 👏🏿 🙏🏿</t>
         </is>
       </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">✋🏿 💪🏿 👐🏿 🙌🏿 👏🏿 🙏🏿</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -1277,6 +2474,13 @@
           <t xml:space="preserve">👨‍👩‍👦 👨‍👩‍👧‍👦 👨‍👨‍👦 👩‍👩‍👧 👨‍👦 👨‍👧‍👦 👩‍👦 👩‍👧‍👦</t>
         </is>
       </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">👨‍👩‍👦 👨‍👩‍👧‍👦 👨‍👨‍👦 👩‍👩‍👧 👨‍👦 👨‍👧‍👦 👩‍👦 👩‍👧‍👦</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -1284,6 +2488,13 @@
           <t xml:space="preserve">🚾 🆒 🆓 🆕 🆖 🆗 🆙 🏧</t>
         </is>
       </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">🚾 🆒 🆓 🆕 🆖 🆗 🆙 🏧</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -1291,6 +2502,13 @@
           <t xml:space="preserve">0️⃣ 1️⃣ 2️⃣ 3️⃣ 4️⃣ 5️⃣ 6️⃣ 7️⃣ 8️⃣ 9️⃣ 🔟</t>
         </is>
       </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0️⃣ 1️⃣ 2️⃣ 3️⃣ 4️⃣ 5️⃣ 6️⃣ 7️⃣ 8️⃣ 9️⃣ 🔟</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -1298,6 +2516,13 @@
           <t xml:space="preserve">🇺🇸🇷🇺🇸 🇦🇫🇦🇲🇸</t>
         </is>
       </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">🇺🇸🇷🇺🇸 🇦🇫🇦🇲🇸</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -1305,6 +2530,13 @@
           <t xml:space="preserve">🇺🇸🇷🇺🇸🇦🇫🇦🇲</t>
         </is>
       </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">🇺🇸🇷🇺🇸🇦🇫🇦🇲</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -1312,6 +2544,13 @@
           <t xml:space="preserve">🇺🇸🇷🇺🇸🇦</t>
         </is>
       </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">🇺🇸🇷🇺🇸🇦</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -1319,6 +2558,13 @@
           <t xml:space="preserve">１２３</t>
         </is>
       </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">１２３</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -1326,6 +2572,13 @@
           <t xml:space="preserve">١٢٣</t>
         </is>
       </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">١٢٣</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -1333,6 +2586,13 @@
           <t xml:space="preserve">ثم نفس سقطت وبالتحديد،, جزيرتي باستخدام أن دنو. إذ هنا؟ الستار وتنصيب كان. أهّل ايطاليا، بريطانيا-فرنسا قد أخذ. سليمان، إتفاقية بين ما, يذكر الحدود أي بعد, معاملة بولندا، الإطلاق عل إيو.</t>
         </is>
       </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ثم نفس سقطت وبالتحديد،, جزيرتي باستخدام أن دنو. إذ هنا؟ الستار وتنصيب كان. أهّل ايطاليا، بريطانيا-فرنسا قد أخذ. سليمان، إتفاقية بين ما, يذكر الحدود أي بعد, معاملة بولندا، الإطلاق عل إيو.</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -1340,6 +2600,13 @@
           <t xml:space="preserve">בְּרֵאשִׁית, בָּרָא אֱלֹהִים, אֵת הַשָּׁמַיִם, וְאֵת הָאָרֶץ</t>
         </is>
       </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">בְּרֵאשִׁית, בָּרָא אֱלֹהִים, אֵת הַשָּׁמַיִם, וְאֵת הָאָרֶץ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -1347,6 +2614,13 @@
           <t xml:space="preserve">הָיְתָהtestالصفحات التّحول</t>
         </is>
       </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">הָיְתָהtestالصفحات التّحول</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -1354,6 +2628,13 @@
           <t xml:space="preserve">﷽</t>
         </is>
       </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">﷽</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -1361,6 +2642,13 @@
           <t xml:space="preserve">ﷺ</t>
         </is>
       </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ﷺ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -1368,6 +2656,13 @@
           <t xml:space="preserve">مُنَاقَشَةُ سُبُلِ اِسْتِخْدَامِ اللُّغَةِ فِي النُّظُمِ الْقَائِمَةِ وَفِيم يَخُصَّ التَّطْبِيقَاتُ الْحاسُوبِيَّةُ،</t>
         </is>
       </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">مُنَاقَشَةُ سُبُلِ اِسْتِخْدَامِ اللُّغَةِ فِي النُّظُمِ الْقَائِمَةِ وَفِيم يَخُصَّ التَّطْبِيقَاتُ الْحاسُوبِيَّةُ،</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -1375,6 +2670,13 @@
           <t xml:space="preserve">الكل في المجمو عة (5)</t>
         </is>
       </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">الكل في المجمو عة (5)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -1382,6 +2684,13 @@
           <t xml:space="preserve">᚛ᚄᚓᚐᚋᚒᚄ ᚑᚄᚂᚑᚏᚅ᚜</t>
         </is>
       </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">᚛ᚄᚓᚐᚋᚒᚄ ᚑᚄᚂᚑᚏᚅ᚜</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -1389,6 +2698,13 @@
           <t xml:space="preserve">᚛                 ᚜</t>
         </is>
       </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">᚛ ᚜</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -1396,6 +2712,13 @@
           <t xml:space="preserve">‪‪test‪</t>
         </is>
       </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">‪‪test‪</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -1403,6 +2726,13 @@
           <t xml:space="preserve">‫test‫</t>
         </is>
       </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">‫test‫</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -1410,6 +2740,13 @@
           <t xml:space="preserve">test</t>
         </is>
       </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">test</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -1417,6 +2754,13 @@
           <t xml:space="preserve">test⁠test‫</t>
         </is>
       </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">test⁠test‫</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -1424,6 +2768,13 @@
           <t xml:space="preserve">⁦test⁧</t>
         </is>
       </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">⁦test⁧</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -1431,6 +2782,13 @@
           <t xml:space="preserve">Ṱ̺̺̕o͞ ̷i̲̬͇̪͙n̝̗͕v̟̜̘̦͟o̶̙̰̠kè͚̮̺̪̹̱̤ ̖t̝͕̳̣̻̪͞h̼͓̲̦̳̘̲e͇̣̰̦̬͎ ̢̼̻̱̘h͚͎͙̜̣̲ͅi̦̲̣̰̤v̻͍e̺̭̳̪̰-m̢iͅn̖̺̞̲̯̰d̵̼̟͙̩̼̘̳ ̞̥̱̳̭r̛̗̘e͙p͠r̼̞̻̭̗e̺̠̣͟s̘͇̳͍̝͉e͉̥̯̞̲͚̬͜ǹ̬͎͎̟̖͇̤t͍̬̤͓̼̭͘ͅi̪̱n͠g̴͉ ͏͉ͅc̬̟h͡a̫̻̯͘o̫̟̖͍̙̝͉s̗̦̲.̨̹͈̣</t>
         </is>
       </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Ṱ̺̺̕o͞ ̷i̲̬͇̪͙n̝̗͕v̟̜̘̦͟o̶̙̰̠kè͚̮̺̪̹̱̤ ̖t̝͕̳̣̻̪͞h̼͓̲̦̳̘̲e͇̣̰̦̬͎ ̢̼̻̱̘h͚͎͙̜̣̲ͅi̦̲̣̰̤v̻͍e̺̭̳̪̰-m̢iͅn̖̺̞̲̯̰d̵̼̟͙̩̼̘̳ ̞̥̱̳̭r̛̗̘e͙p͠r̼̞̻̭̗e̺̠̣͟s̘͇̳͍̝͉e͉̥̯̞̲͚̬͜ǹ̬͎͎̟̖͇̤t͍̬̤͓̼̭͘ͅi̪̱n͠g̴͉ ͏͉ͅc̬̟h͡a̫̻̯͘o̫̟̖͍̙̝͉s̗̦̲.̨̹͈̣</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -1438,6 +2796,13 @@
           <t xml:space="preserve">̡͓̞ͅI̗̘̦͝n͇͇͙v̮̫ok̲̫̙͈i̖͙̭̹̠̞n̡̻̮̣̺g̲͈͙̭͙̬͎ ̰t͔̦h̞̲e̢̤ ͍̬̲͖f̴̘͕̣è͖ẹ̥̩l͖͔͚i͓͚̦͠n͖͍̗͓̳̮g͍ ̨o͚̪͡f̘̣̬ ̖̘͖̟͙̮c҉͔̫͖͓͇͖ͅh̵̤̣͚͔á̗̼͕ͅo̼̣̥s̱͈̺̖̦̻͢.̛̖̞̠̫̰</t>
         </is>
       </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">̡͓̞ͅI̗̘̦͝n͇͇͙v̮̫ok̲̫̙͈i̖͙̭̹̠̞n̡̻̮̣̺g̲͈͙̭͙̬͎ ̰t͔̦h̞̲e̢̤ ͍̬̲͖f̴̘͕̣è͖ẹ̥̩l͖͔͚i͓͚̦͠n͖͍̗͓̳̮g͍ ̨o͚̪͡f̘̣̬ ̖̘͖̟͙̮c҉͔̫͖͓͇͖ͅh̵̤̣͚͔á̗̼͕ͅo̼̣̥s̱͈̺̖̦̻͢.̛̖̞̠̫̰</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -1445,6 +2810,13 @@
           <t xml:space="preserve">̗̺͖̹̯͓Ṯ̤͍̥͇͈h̲́e͏͓̼̗̙̼̣͔ ͇̜̱̠͓͍ͅN͕͠e̗̱z̘̝̜̺͙p̤̺̹͍̯͚e̠̻̠͜r̨̤͍̺̖͔̖̖d̠̟̭̬̝͟i̦͖̩͓͔̤a̠̗̬͉̙n͚͜ ̻̞̰͚ͅh̵͉i̳̞v̢͇ḙ͎͟-҉̭̩̼͔m̤̭̫i͕͇̝̦n̗͙ḍ̟ ̯̲͕͞ǫ̟̯̰̲͙̻̝f ̪̰̰̗̖̭̘͘c̦͍̲̞͍̩̙ḥ͚a̮͎̟̙͜ơ̩̹͎s̤.̝̝ ҉Z̡̖̜͖̰̣͉̜a͖̰͙̬͡l̲̫̳͍̩g̡̟̼̱͚̞̬ͅo̗͜.̟</t>
         </is>
       </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">̗̺͖̹̯͓Ṯ̤͍̥͇͈h̲́e͏͓̼̗̙̼̣͔ ͇̜̱̠͓͍ͅN͕͠e̗̱z̘̝̜̺͙p̤̺̹͍̯͚e̠̻̠͜r̨̤͍̺̖͔̖̖d̠̟̭̬̝͟i̦͖̩͓͔̤a̠̗̬͉̙n͚͜ ̻̞̰͚ͅh̵͉i̳̞v̢͇ḙ͎͟-҉̭̩̼͔m̤̭̫i͕͇̝̦n̗͙ḍ̟ ̯̲͕͞ǫ̟̯̰̲͙̻̝f ̪̰̰̗̖̭̘͘c̦͍̲̞͍̩̙ḥ͚a̮͎̟̙͜ơ̩̹͎s̤.̝̝ ҉Z̡̖̜͖̰̣͉̜a͖̰͙̬͡l̲̫̳͍̩g̡̟̼̱͚̞̬ͅo̗͜.̟</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -1452,6 +2824,13 @@
           <t xml:space="preserve">̦H̬̤̗̤͝e͜ ̜̥̝̻͍̟́w̕h̖̯͓o̝͙̖͎̱̮ ҉̺̙̞̟͈W̷̼̭a̺̪͍į͈͕̭͙̯̜t̶̼̮s̘͙͖̕ ̠̫̠B̻͍͙͉̳ͅe̵h̵̬͇̫͙i̹͓̳̳̮͎̫̕n͟d̴̪̜̖ ̰͉̩͇͙̲͞ͅT͖̼͓̪͢h͏͓̮̻e̬̝̟ͅ ̤̹̝W͙̞̝͔͇͝ͅa͏͓͔̹̼̣l̴͔̰̤̟͔ḽ̫.͕</t>
         </is>
       </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">̦H̬̤̗̤͝e͜ ̜̥̝̻͍̟́w̕h̖̯͓o̝͙̖͎̱̮ ҉̺̙̞̟͈W̷̼̭a̺̪͍į͈͕̭͙̯̜t̶̼̮s̘͙͖̕ ̠̫̠B̻͍͙͉̳ͅe̵h̵̬͇̫͙i̹͓̳̳̮͎̫̕n͟d̴̪̜̖ ̰͉̩͇͙̲͞ͅT͖̼͓̪͢h͏͓̮̻e̬̝̟ͅ ̤̹̝W͙̞̝͔͇͝ͅa͏͓͔̹̼̣l̴͔̰̤̟͔ḽ̫.͕</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -1459,6 +2838,13 @@
           <t xml:space="preserve">Z̮̞̠͙͔ͅḀ̗̞͈̻̗Ḷ͙͎̯̹̞͓G̻O̭̗̮</t>
         </is>
       </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Z̮̞̠͙͔ͅḀ̗̞͈̻̗Ḷ͙͎̯̹̞͓G̻O̭̗̮</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -1466,6 +2852,13 @@
           <t xml:space="preserve">˙ɐnbᴉlɐ ɐuƃɐɯ ǝɹolop ʇǝ ǝɹoqɐl ʇn ʇunpᴉpᴉɔuᴉ ɹodɯǝʇ poɯsnᴉǝ op pǝs 'ʇᴉlǝ ƃuᴉɔsᴉdᴉpɐ ɹnʇǝʇɔǝsuoɔ 'ʇǝɯɐ ʇᴉs ɹolop ɯnsdᴉ ɯǝɹo˥</t>
         </is>
       </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">˙ɐnbᴉlɐ ɐuƃɐɯ ǝɹolop ʇǝ ǝɹoqɐl ʇn ʇunpᴉpᴉɔuᴉ ɹodɯǝʇ poɯsnᴉǝ op pǝs 'ʇᴉlǝ ƃuᴉɔsᴉdᴉpɐ ɹnʇǝʇɔǝsuoɔ 'ʇǝɯɐ ʇᴉs ɹolop ɯnsdᴉ ɯǝɹo˥</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -1473,6 +2866,13 @@
           <t xml:space="preserve">00˙Ɩ$-</t>
         </is>
       </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">00˙Ɩ$-</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -1480,6 +2880,13 @@
           <t xml:space="preserve">Ｔｈｅ ｑｕｉｃｋ ｂｒｏｗｎ ｆｏｘ ｊｕｍｐｓ ｏｖｅｒ ｔｈｅ ｌａｚｙ ｄｏｇ</t>
         </is>
       </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Ｔｈｅ ｑｕｉｃｋ ｂｒｏｗｎ ｆｏｘ ｊｕｍｐｓ ｏｖｅｒ ｔｈｅ ｌａｚｙ ｄｏｇ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -1487,6 +2894,13 @@
           <t xml:space="preserve">𝐓𝐡𝐞 𝐪𝐮𝐢𝐜𝐤 𝐛𝐫𝐨𝐰𝐧 𝐟𝐨𝐱 𝐣𝐮𝐦𝐩𝐬 𝐨𝐯𝐞𝐫 𝐭𝐡𝐞 𝐥𝐚𝐳𝐲 𝐝𝐨𝐠</t>
         </is>
       </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">𝐓𝐡𝐞 𝐪𝐮𝐢𝐜𝐤 𝐛𝐫𝐨𝐰𝐧 𝐟𝐨𝐱 𝐣𝐮𝐦𝐩𝐬 𝐨𝐯𝐞𝐫 𝐭𝐡𝐞 𝐥𝐚𝐳𝐲 𝐝𝐨𝐠</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -1494,6 +2908,13 @@
           <t xml:space="preserve">𝕿𝖍𝖊 𝖖𝖚𝖎𝖈𝖐 𝖇𝖗𝖔𝖜𝖓 𝖋𝖔𝖝 𝖏𝖚𝖒𝖕𝖘 𝖔𝖛𝖊𝖗 𝖙𝖍𝖊 𝖑𝖆𝖟𝖞 𝖉𝖔𝖌</t>
         </is>
       </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">𝕿𝖍𝖊 𝖖𝖚𝖎𝖈𝖐 𝖇𝖗𝖔𝖜𝖓 𝖋𝖔𝖝 𝖏𝖚𝖒𝖕𝖘 𝖔𝖛𝖊𝖗 𝖙𝖍𝖊 𝖑𝖆𝖟𝖞 𝖉𝖔𝖌</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -1501,6 +2922,13 @@
           <t xml:space="preserve">𝑻𝒉𝒆 𝒒𝒖𝒊𝒄𝒌 𝒃𝒓𝒐𝒘𝒏 𝒇𝒐𝒙 𝒋𝒖𝒎𝒑𝒔 𝒐𝒗𝒆𝒓 𝒕𝒉𝒆 𝒍𝒂𝒛𝒚 𝒅𝒐𝒈</t>
         </is>
       </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">𝑻𝒉𝒆 𝒒𝒖𝒊𝒄𝒌 𝒃𝒓𝒐𝒘𝒏 𝒇𝒐𝒙 𝒋𝒖𝒎𝒑𝒔 𝒐𝒗𝒆𝒓 𝒕𝒉𝒆 𝒍𝒂𝒛𝒚 𝒅𝒐𝒈</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -1508,6 +2936,13 @@
           <t xml:space="preserve">𝓣𝓱𝓮 𝓺𝓾𝓲𝓬𝓴 𝓫𝓻𝓸𝔀𝓷 𝓯𝓸𝔁 𝓳𝓾𝓶𝓹𝓼 𝓸𝓿𝓮𝓻 𝓽𝓱𝓮 𝓵𝓪𝔃𝔂 𝓭𝓸𝓰</t>
         </is>
       </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">𝓣𝓱𝓮 𝓺𝓾𝓲𝓬𝓴 𝓫𝓻𝓸𝔀𝓷 𝓯𝓸𝔁 𝓳𝓾𝓶𝓹𝓼 𝓸𝓿𝓮𝓻 𝓽𝓱𝓮 𝓵𝓪𝔃𝔂 𝓭𝓸𝓰</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -1515,6 +2950,13 @@
           <t xml:space="preserve">𝕋𝕙𝕖 𝕢𝕦𝕚𝕔𝕜 𝕓𝕣𝕠𝕨𝕟 𝕗𝕠𝕩 𝕛𝕦𝕞𝕡𝕤 𝕠𝕧𝕖𝕣 𝕥𝕙𝕖 𝕝𝕒𝕫𝕪 𝕕𝕠𝕘</t>
         </is>
       </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">𝕋𝕙𝕖 𝕢𝕦𝕚𝕔𝕜 𝕓𝕣𝕠𝕨𝕟 𝕗𝕠𝕩 𝕛𝕦𝕞𝕡𝕤 𝕠𝕧𝕖𝕣 𝕥𝕙𝕖 𝕝𝕒𝕫𝕪 𝕕𝕠𝕘</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -1522,6 +2964,13 @@
           <t xml:space="preserve">𝚃𝚑𝚎 𝚚𝚞𝚒𝚌𝚔 𝚋𝚛𝚘𝚠𝚗 𝚏𝚘𝚡 𝚓𝚞𝚖𝚙𝚜 𝚘𝚟𝚎𝚛 𝚝𝚑𝚎 𝚕𝚊𝚣𝚢 𝚍𝚘𝚐</t>
         </is>
       </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">𝚃𝚑𝚎 𝚚𝚞𝚒𝚌𝚔 𝚋𝚛𝚘𝚠𝚗 𝚏𝚘𝚡 𝚓𝚞𝚖𝚙𝚜 𝚘𝚟𝚎𝚛 𝚝𝚑𝚎 𝚕𝚊𝚣𝚢 𝚍𝚘𝚐</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -1529,6 +2978,13 @@
           <t xml:space="preserve">⒯⒣⒠ ⒬⒰⒤⒞⒦ ⒝⒭⒪⒲⒩ ⒡⒪⒳ ⒥⒰⒨⒫⒮ ⒪⒱⒠⒭ ⒯⒣⒠ ⒧⒜⒵⒴ ⒟⒪⒢</t>
         </is>
       </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">⒯⒣⒠ ⒬⒰⒤⒞⒦ ⒝⒭⒪⒲⒩ ⒡⒪⒳ ⒥⒰⒨⒫⒮ ⒪⒱⒠⒭ ⒯⒣⒠ ⒧⒜⒵⒴ ⒟⒪⒢</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -1536,6 +2992,13 @@
           <t xml:space="preserve">&lt;script&gt;alert(0)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">alert(0)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -1543,6 +3006,13 @@
           <t xml:space="preserve">&amp;lt;script&amp;gt;alert(&amp;#39;1&amp;#39;);&amp;lt;/script&amp;gt;</t>
         </is>
       </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">&lt;script&gt;alert('1');&lt;/script&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -1550,6 +3020,9 @@
           <t xml:space="preserve">&lt;img src=x onerror=alert(2) /&gt;</t>
         </is>
       </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -1557,6 +3030,9 @@
           <t xml:space="preserve">&lt;svg&gt;&lt;script&gt;123&lt;1&gt;alert(3)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -1564,6 +3040,16 @@
           <t xml:space="preserve">"&gt;&lt;script&gt;alert(4)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">alert(4)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -1571,6 +3057,16 @@
           <t xml:space="preserve">'&gt;&lt;script&gt;alert(5)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">alert(5)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -1578,6 +3074,16 @@
           <t xml:space="preserve">&gt;&lt;script&gt;alert(6)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">alert(6)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -1585,6 +3091,13 @@
           <t xml:space="preserve">&lt;/script&gt;&lt;script&gt;alert(7)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">alert(7)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -1592,6 +3105,13 @@
           <t xml:space="preserve">&lt; / script &gt;&lt; script &gt;alert(8)&lt; / script &gt;</t>
         </is>
       </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">&lt; / script &gt;&lt; script &gt;alert(8)&lt; / script &gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -1599,6 +3119,13 @@
           <t xml:space="preserve">onfocus=JaVaSCript:alert(9) autofocus</t>
         </is>
       </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">onfocus=JaVaSCript:alert(9) autofocus</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -1606,6 +3133,13 @@
           <t xml:space="preserve">" onfocus=JaVaSCript:alert(10) autofocus</t>
         </is>
       </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">" onfocus=JaVaSCript:alert(10) autofocus</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -1613,6 +3147,13 @@
           <t xml:space="preserve">' onfocus=JaVaSCript:alert(11) autofocus</t>
         </is>
       </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">' onfocus=JaVaSCript:alert(11) autofocus</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -1620,6 +3161,13 @@
           <t xml:space="preserve">＜script＞alert(12)＜/script＞</t>
         </is>
       </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">＜script＞alert(12)＜/script＞</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -1627,6 +3175,13 @@
           <t xml:space="preserve">&lt;sc&lt;script&gt;ript&gt;alert(13)&lt;/sc&lt;/script&gt;ript&gt;</t>
         </is>
       </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ript&gt;alert(13)ript&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -1634,6 +3189,16 @@
           <t xml:space="preserve">--&gt;&lt;script&gt;alert(14)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">--&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">alert(14)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -1641,6 +3206,13 @@
           <t xml:space="preserve">";alert(15);t="</t>
         </is>
       </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">";alert(15);t="</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -1648,6 +3220,13 @@
           <t xml:space="preserve">';alert(16);t='</t>
         </is>
       </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">';alert(16);t='</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -1655,6 +3234,13 @@
           <t xml:space="preserve">JavaSCript:alert(17)</t>
         </is>
       </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">JavaSCript:alert(17)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -1662,6 +3248,13 @@
           <t xml:space="preserve">;alert(18);</t>
         </is>
       </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">;alert(18);</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -1669,6 +3262,13 @@
           <t xml:space="preserve">src=JaVaSCript:prompt(19)</t>
         </is>
       </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">src=JaVaSCript:prompt(19)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -1676,6 +3276,16 @@
           <t xml:space="preserve">"&gt;&lt;script&gt;alert(20);&lt;/script x="</t>
         </is>
       </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">alert(20);</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -1683,6 +3293,16 @@
           <t xml:space="preserve">'&gt;&lt;script&gt;alert(21);&lt;/script x='</t>
         </is>
       </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">alert(21);</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -1690,6 +3310,16 @@
           <t xml:space="preserve">&gt;&lt;script&gt;alert(22);&lt;/script x=</t>
         </is>
       </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">alert(22);</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -1697,6 +3327,13 @@
           <t xml:space="preserve">" autofocus onkeyup="javascript:alert(23)</t>
         </is>
       </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">" autofocus onkeyup="javascript:alert(23)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -1704,6 +3341,13 @@
           <t xml:space="preserve">' autofocus onkeyup='javascript:alert(24)</t>
         </is>
       </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">' autofocus onkeyup='javascript:alert(24)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -1711,6 +3355,13 @@
           <t xml:space="preserve">&lt;script\x20type="text/javascript"&gt;javascript:alert(25);&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">javascript:alert(25);</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -1718,6 +3369,13 @@
           <t xml:space="preserve">&lt;script\x3Etype="text/javascript"&gt;javascript:alert(26);&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">javascript:alert(26);</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -1725,6 +3383,13 @@
           <t xml:space="preserve">&lt;script\x0Dtype="text/javascript"&gt;javascript:alert(27);&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">javascript:alert(27);</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -1732,6 +3397,13 @@
           <t xml:space="preserve">&lt;script\x09type="text/javascript"&gt;javascript:alert(28);&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">javascript:alert(28);</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -1739,6 +3411,13 @@
           <t xml:space="preserve">&lt;script\x0Ctype="text/javascript"&gt;javascript:alert(29);&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">javascript:alert(29);</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -1746,6 +3425,13 @@
           <t xml:space="preserve">&lt;script\x2Ftype="text/javascript"&gt;javascript:alert(30);&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">javascript:alert(30);</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -1753,6 +3439,13 @@
           <t xml:space="preserve">&lt;script\x0Atype="text/javascript"&gt;javascript:alert(31);&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">javascript:alert(31);</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -1760,6 +3453,13 @@
           <t xml:space="preserve">'`"&gt;&lt;\x3Cscript&gt;javascript:alert(32)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">'`"&gt;&lt;\x3Cscript&gt;javascript:alert(32)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -1767,6 +3467,13 @@
           <t xml:space="preserve">'`"&gt;&lt;\x00script&gt;javascript:alert(33)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">'`"&gt;&lt;\x00script&gt;javascript:alert(33)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -1774,6 +3481,20 @@
           <t xml:space="preserve">ABC&lt;div style="x\x3Aexpression(javascript:alert(34)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -1781,6 +3502,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:expression\x5C(javascript:alert(35)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -1788,6 +3523,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:expression\x00(javascript:alert(36)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -1795,6 +3544,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:exp\x00ression(javascript:alert(37)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -1802,6 +3565,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:exp\x5Cression(javascript:alert(38)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -1809,6 +3586,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\x0Aexpression(javascript:alert(39)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -1816,6 +3607,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\x09expression(javascript:alert(40)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -1823,6 +3628,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\xE3\x80\x80expression(javascript:alert(41)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -1830,6 +3649,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\xE2\x80\x84expression(javascript:alert(42)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -1837,6 +3670,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\xC2\xA0expression(javascript:alert(43)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -1844,6 +3691,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\xE2\x80\x80expression(javascript:alert(44)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -1851,6 +3712,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\xE2\x80\x8Aexpression(javascript:alert(45)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -1858,6 +3733,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\x0Dexpression(javascript:alert(46)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -1865,6 +3754,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\x0Cexpression(javascript:alert(47)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -1872,6 +3775,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\xE2\x80\x87expression(javascript:alert(48)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -1879,6 +3796,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\xEF\xBB\xBFexpression(javascript:alert(49)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -1886,6 +3817,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\x20expression(javascript:alert(50)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -1893,6 +3838,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\xE2\x80\x88expression(javascript:alert(51)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -1900,6 +3859,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\x00expression(javascript:alert(52)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -1907,6 +3880,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\xE2\x80\x8Bexpression(javascript:alert(53)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -1914,6 +3901,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\xE2\x80\x86expression(javascript:alert(54)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -1921,6 +3922,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\xE2\x80\x85expression(javascript:alert(55)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -1928,6 +3943,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\xE2\x80\x82expression(javascript:alert(56)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -1935,6 +3964,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\x0Bexpression(javascript:alert(57)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -1942,6 +3985,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\xE2\x80\x81expression(javascript:alert(58)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -1949,6 +4006,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\xE2\x80\x83expression(javascript:alert(59)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -1956,6 +4027,20 @@
           <t xml:space="preserve">ABC&lt;div style="x:\xE2\x80\x89expression(javascript:alert(60)"&gt;DEF</t>
         </is>
       </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ABC</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+</t>
+          </r>
+          <r>
+            <t xml:space="preserve">DEF</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -1963,6 +4048,20 @@
           <t xml:space="preserve">&lt;a href="\x0Bjavascript:javascript:alert(61)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x0Bjavascript:javascript:alert(61))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -1970,6 +4069,20 @@
           <t xml:space="preserve">&lt;a href="\x0Fjavascript:javascript:alert(62)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x0Fjavascript:javascript:alert(62))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -1977,6 +4090,20 @@
           <t xml:space="preserve">&lt;a href="\xC2\xA0javascript:javascript:alert(63)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xC2\xA0javascript:javascript:alert(63))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -1984,6 +4111,20 @@
           <t xml:space="preserve">&lt;a href="\x05javascript:javascript:alert(64)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x05javascript:javascript:alert(64))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -1991,6 +4132,20 @@
           <t xml:space="preserve">&lt;a href="\xE1\xA0\x8Ejavascript:javascript:alert(65)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE1\xA0\x8Ejavascript:javascript:alert(65))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -1998,6 +4153,20 @@
           <t xml:space="preserve">&lt;a href="\x18javascript:javascript:alert(66)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x18javascript:javascript:alert(66))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -2005,6 +4174,20 @@
           <t xml:space="preserve">&lt;a href="\x11javascript:javascript:alert(67)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x11javascript:javascript:alert(67))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -2012,6 +4195,20 @@
           <t xml:space="preserve">&lt;a href="\xE2\x80\x88javascript:javascript:alert(68)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE2\x80\x88javascript:javascript:alert(68))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -2019,6 +4216,20 @@
           <t xml:space="preserve">&lt;a href="\xE2\x80\x89javascript:javascript:alert(69)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE2\x80\x89javascript:javascript:alert(69))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -2026,6 +4237,20 @@
           <t xml:space="preserve">&lt;a href="\xE2\x80\x80javascript:javascript:alert(70)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE2\x80\x80javascript:javascript:alert(70))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -2033,6 +4258,20 @@
           <t xml:space="preserve">&lt;a href="\x17javascript:javascript:alert(71)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x17javascript:javascript:alert(71))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -2040,6 +4279,20 @@
           <t xml:space="preserve">&lt;a href="\x03javascript:javascript:alert(72)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x03javascript:javascript:alert(72))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -2047,6 +4300,20 @@
           <t xml:space="preserve">&lt;a href="\x0Ejavascript:javascript:alert(73)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x0Ejavascript:javascript:alert(73))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -2054,6 +4321,20 @@
           <t xml:space="preserve">&lt;a href="\x1Ajavascript:javascript:alert(74)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x1Ajavascript:javascript:alert(74))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -2061,6 +4342,20 @@
           <t xml:space="preserve">&lt;a href="\x00javascript:javascript:alert(75)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x00javascript:javascript:alert(75))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -2068,6 +4363,20 @@
           <t xml:space="preserve">&lt;a href="\x10javascript:javascript:alert(76)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x10javascript:javascript:alert(76))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -2075,6 +4384,20 @@
           <t xml:space="preserve">&lt;a href="\xE2\x80\x82javascript:javascript:alert(77)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE2\x80\x82javascript:javascript:alert(77))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -2082,6 +4405,20 @@
           <t xml:space="preserve">&lt;a href="\x20javascript:javascript:alert(78)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x20javascript:javascript:alert(78))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -2089,6 +4426,20 @@
           <t xml:space="preserve">&lt;a href="\x13javascript:javascript:alert(79)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x13javascript:javascript:alert(79))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -2096,6 +4447,20 @@
           <t xml:space="preserve">&lt;a href="\x09javascript:javascript:alert(80)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x09javascript:javascript:alert(80))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -2103,6 +4468,20 @@
           <t xml:space="preserve">&lt;a href="\xE2\x80\x8Ajavascript:javascript:alert(81)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE2\x80\x8Ajavascript:javascript:alert(81))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -2110,6 +4489,20 @@
           <t xml:space="preserve">&lt;a href="\x14javascript:javascript:alert(82)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x14javascript:javascript:alert(82))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -2117,6 +4510,20 @@
           <t xml:space="preserve">&lt;a href="\x19javascript:javascript:alert(83)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x19javascript:javascript:alert(83))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -2124,6 +4531,20 @@
           <t xml:space="preserve">&lt;a href="\xE2\x80\xAFjavascript:javascript:alert(84)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE2\x80\xAFjavascript:javascript:alert(84))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -2131,6 +4552,20 @@
           <t xml:space="preserve">&lt;a href="\x1Fjavascript:javascript:alert(85)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x1Fjavascript:javascript:alert(85))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -2138,6 +4573,20 @@
           <t xml:space="preserve">&lt;a href="\xE2\x80\x81javascript:javascript:alert(86)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE2\x80\x81javascript:javascript:alert(86))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -2145,6 +4594,20 @@
           <t xml:space="preserve">&lt;a href="\x1Djavascript:javascript:alert(87)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x1Djavascript:javascript:alert(87))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -2152,6 +4615,20 @@
           <t xml:space="preserve">&lt;a href="\xE2\x80\x87javascript:javascript:alert(88)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE2\x80\x87javascript:javascript:alert(88))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -2159,6 +4636,20 @@
           <t xml:space="preserve">&lt;a href="\x07javascript:javascript:alert(89)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x07javascript:javascript:alert(89))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -2166,6 +4657,20 @@
           <t xml:space="preserve">&lt;a href="\xE1\x9A\x80javascript:javascript:alert(90)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE1\x9A\x80javascript:javascript:alert(90))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -2173,6 +4678,20 @@
           <t xml:space="preserve">&lt;a href="\xE2\x80\x83javascript:javascript:alert(91)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE2\x80\x83javascript:javascript:alert(91))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -2180,6 +4699,20 @@
           <t xml:space="preserve">&lt;a href="\x04javascript:javascript:alert(92)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x04javascript:javascript:alert(92))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -2187,6 +4720,20 @@
           <t xml:space="preserve">&lt;a href="\x01javascript:javascript:alert(93)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x01javascript:javascript:alert(93))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -2194,6 +4741,20 @@
           <t xml:space="preserve">&lt;a href="\x08javascript:javascript:alert(94)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x08javascript:javascript:alert(94))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -2201,6 +4762,20 @@
           <t xml:space="preserve">&lt;a href="\xE2\x80\x84javascript:javascript:alert(95)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE2\x80\x84javascript:javascript:alert(95))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -2208,6 +4783,20 @@
           <t xml:space="preserve">&lt;a href="\xE2\x80\x86javascript:javascript:alert(96)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE2\x80\x86javascript:javascript:alert(96))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -2215,6 +4804,20 @@
           <t xml:space="preserve">&lt;a href="\xE3\x80\x80javascript:javascript:alert(97)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE3\x80\x80javascript:javascript:alert(97))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -2222,6 +4825,20 @@
           <t xml:space="preserve">&lt;a href="\x12javascript:javascript:alert(98)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x12javascript:javascript:alert(98))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -2229,6 +4846,20 @@
           <t xml:space="preserve">&lt;a href="\x0Djavascript:javascript:alert(99)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x0Djavascript:javascript:alert(99))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -2236,6 +4867,20 @@
           <t xml:space="preserve">&lt;a href="\x0Ajavascript:javascript:alert(100)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x0Ajavascript:javascript:alert(100))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -2243,6 +4888,20 @@
           <t xml:space="preserve">&lt;a href="\x0Cjavascript:javascript:alert(101)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x0Cjavascript:javascript:alert(101))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -2250,6 +4909,20 @@
           <t xml:space="preserve">&lt;a href="\x15javascript:javascript:alert(102)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x15javascript:javascript:alert(102))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -2257,6 +4930,20 @@
           <t xml:space="preserve">&lt;a href="\xE2\x80\xA8javascript:javascript:alert(103)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE2\x80\xA8javascript:javascript:alert(103))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -2264,6 +4951,20 @@
           <t xml:space="preserve">&lt;a href="\x16javascript:javascript:alert(104)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x16javascript:javascript:alert(104))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -2271,6 +4972,20 @@
           <t xml:space="preserve">&lt;a href="\x02javascript:javascript:alert(105)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x02javascript:javascript:alert(105))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -2278,6 +4993,20 @@
           <t xml:space="preserve">&lt;a href="\x1Bjavascript:javascript:alert(106)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x1Bjavascript:javascript:alert(106))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -2285,6 +5014,20 @@
           <t xml:space="preserve">&lt;a href="\x06javascript:javascript:alert(107)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x06javascript:javascript:alert(107))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -2292,6 +5035,20 @@
           <t xml:space="preserve">&lt;a href="\xE2\x80\xA9javascript:javascript:alert(108)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE2\x80\xA9javascript:javascript:alert(108))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -2299,6 +5056,20 @@
           <t xml:space="preserve">&lt;a href="\xE2\x80\x85javascript:javascript:alert(109)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE2\x80\x85javascript:javascript:alert(109))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -2306,6 +5077,20 @@
           <t xml:space="preserve">&lt;a href="\x1Ejavascript:javascript:alert(110)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x1Ejavascript:javascript:alert(110))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -2313,6 +5098,20 @@
           <t xml:space="preserve">&lt;a href="\xE2\x81\x9Fjavascript:javascript:alert(111)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\xE2\x81\x9Fjavascript:javascript:alert(111))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -2320,6 +5119,20 @@
           <t xml:space="preserve">&lt;a href="\x1Cjavascript:javascript:alert(112)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (\x1Cjavascript:javascript:alert(112))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -2327,6 +5140,20 @@
           <t xml:space="preserve">&lt;a href="javascript\x00:javascript:alert(113)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (javascript\x00:javascript:alert(113))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -2334,6 +5161,20 @@
           <t xml:space="preserve">&lt;a href="javascript\x3A:javascript:alert(114)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (javascript\x3A:javascript:alert(114))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -2341,6 +5182,20 @@
           <t xml:space="preserve">&lt;a href="javascript\x09:javascript:alert(115)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (javascript\x09:javascript:alert(115))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -2348,6 +5203,20 @@
           <t xml:space="preserve">&lt;a href="javascript\x0D:javascript:alert(116)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (javascript\x0D:javascript:alert(116))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -2355,6 +5224,20 @@
           <t xml:space="preserve">&lt;a href="javascript\x0A:javascript:alert(117)" id="fuzzelement1"&gt;test&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">test</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (javascript\x0A:javascript:alert(117))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -2362,6 +5245,13 @@
           <t xml:space="preserve">`"'&gt;&lt;img src=xxx:x \x0Aonerror=javascript:alert(118)&gt;</t>
         </is>
       </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">`"'&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -2369,6 +5259,13 @@
           <t xml:space="preserve">`"'&gt;&lt;img src=xxx:x \x22onerror=javascript:alert(119)&gt;</t>
         </is>
       </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">`"'&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -2376,6 +5273,13 @@
           <t xml:space="preserve">`"'&gt;&lt;img src=xxx:x \x0Bonerror=javascript:alert(120)&gt;</t>
         </is>
       </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">`"'&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -2383,6 +5287,13 @@
           <t xml:space="preserve">`"'&gt;&lt;img src=xxx:x \x0Donerror=javascript:alert(121)&gt;</t>
         </is>
       </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">`"'&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -2390,6 +5301,13 @@
           <t xml:space="preserve">`"'&gt;&lt;img src=xxx:x \x2Fonerror=javascript:alert(122)&gt;</t>
         </is>
       </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">`"'&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -2397,6 +5315,13 @@
           <t xml:space="preserve">`"'&gt;&lt;img src=xxx:x \x09onerror=javascript:alert(123)&gt;</t>
         </is>
       </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">`"'&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -2404,6 +5329,13 @@
           <t xml:space="preserve">`"'&gt;&lt;img src=xxx:x \x0Conerror=javascript:alert(124)&gt;</t>
         </is>
       </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">`"'&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -2411,6 +5343,13 @@
           <t xml:space="preserve">`"'&gt;&lt;img src=xxx:x \x00onerror=javascript:alert(125)&gt;</t>
         </is>
       </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">`"'&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -2418,6 +5357,13 @@
           <t xml:space="preserve">`"'&gt;&lt;img src=xxx:x \x27onerror=javascript:alert(126)&gt;</t>
         </is>
       </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">`"'&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -2425,6 +5371,13 @@
           <t xml:space="preserve">`"'&gt;&lt;img src=xxx:x \x20onerror=javascript:alert(127)&gt;</t>
         </is>
       </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">`"'&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -2432,6 +5385,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\x3Bjavascript:alert(128)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\x3Bjavascript:alert(128)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -2439,6 +5402,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\x0Djavascript:alert(129)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\x0Djavascript:alert(129)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -2446,6 +5419,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xEF\xBB\xBFjavascript:alert(130)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xEF\xBB\xBFjavascript:alert(130)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -2453,6 +5436,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE2\x80\x81javascript:alert(131)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE2\x80\x81javascript:alert(131)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -2460,6 +5453,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE2\x80\x84javascript:alert(132)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE2\x80\x84javascript:alert(132)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -2467,6 +5470,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE3\x80\x80javascript:alert(133)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE3\x80\x80javascript:alert(133)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -2474,6 +5487,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\x09javascript:alert(134)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\x09javascript:alert(134)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -2481,6 +5504,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE2\x80\x89javascript:alert(135)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE2\x80\x89javascript:alert(135)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -2488,6 +5521,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE2\x80\x85javascript:alert(136)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE2\x80\x85javascript:alert(136)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -2495,6 +5538,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE2\x80\x88javascript:alert(137)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE2\x80\x88javascript:alert(137)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -2502,6 +5555,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\x00javascript:alert(138)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\x00javascript:alert(138)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -2509,6 +5572,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE2\x80\xA8javascript:alert(139)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE2\x80\xA8javascript:alert(139)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -2516,6 +5589,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE2\x80\x8Ajavascript:alert(140)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE2\x80\x8Ajavascript:alert(140)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -2523,6 +5606,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE1\x9A\x80javascript:alert(141)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE1\x9A\x80javascript:alert(141)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -2530,6 +5623,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\x0Cjavascript:alert(142)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\x0Cjavascript:alert(142)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -2537,6 +5640,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\x2Bjavascript:alert(143)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\x2Bjavascript:alert(143)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -2544,6 +5657,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xF0\x90\x96\x9Ajavascript:alert(144)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xF0\x90\x96\x9Ajavascript:alert(144)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -2551,6 +5674,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;-javascript:alert(145)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">-javascript:alert(145)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -2558,6 +5691,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\x0Ajavascript:alert(146)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\x0Ajavascript:alert(146)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -2565,6 +5708,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE2\x80\xAFjavascript:alert(147)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE2\x80\xAFjavascript:alert(147)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -2572,6 +5725,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\x7Ejavascript:alert(148)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\x7Ejavascript:alert(148)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -2579,6 +5742,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE2\x80\x87javascript:alert(149)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE2\x80\x87javascript:alert(149)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -2586,6 +5759,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE2\x81\x9Fjavascript:alert(150)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE2\x81\x9Fjavascript:alert(150)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -2593,6 +5776,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE2\x80\xA9javascript:alert(151)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE2\x80\xA9javascript:alert(151)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -2600,6 +5793,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xC2\x85javascript:alert(152)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xC2\x85javascript:alert(152)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -2607,6 +5810,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xEF\xBF\xAEjavascript:alert(153)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xEF\xBF\xAEjavascript:alert(153)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -2614,6 +5827,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE2\x80\x83javascript:alert(154)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE2\x80\x83javascript:alert(154)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -2621,6 +5844,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE2\x80\x8Bjavascript:alert(155)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE2\x80\x8Bjavascript:alert(155)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -2628,6 +5861,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xEF\xBF\xBEjavascript:alert(156)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xEF\xBF\xBEjavascript:alert(156)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -2635,6 +5878,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE2\x80\x80javascript:alert(157)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE2\x80\x80javascript:alert(157)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -2642,6 +5895,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\x21javascript:alert(158)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\x21javascript:alert(158)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -2649,6 +5912,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE2\x80\x82javascript:alert(159)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE2\x80\x82javascript:alert(159)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -2656,6 +5929,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE2\x80\x86javascript:alert(160)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE2\x80\x86javascript:alert(160)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -2663,6 +5946,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xE1\xA0\x8Ejavascript:alert(161)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xE1\xA0\x8Ejavascript:alert(161)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -2670,6 +5963,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\x0Bjavascript:alert(162)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\x0Bjavascript:alert(162)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -2677,6 +5980,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\x20javascript:alert(163)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\x20javascript:alert(163)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -2684,6 +5997,16 @@
           <t xml:space="preserve">"`'&gt;&lt;script&gt;\xC2\xA0javascript:alert(164)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">"`'&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">\xC2\xA0javascript:alert(164)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -2691,6 +6014,9 @@
           <t xml:space="preserve">&lt;img \x00src=x onerror="alert(165)"&gt;</t>
         </is>
       </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -2698,6 +6024,9 @@
           <t xml:space="preserve">&lt;img \x47src=x onerror="javascript:alert(166)"&gt;</t>
         </is>
       </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -2705,6 +6034,9 @@
           <t xml:space="preserve">&lt;img \x11src=x onerror="javascript:alert(167)"&gt;</t>
         </is>
       </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -2712,6 +6044,9 @@
           <t xml:space="preserve">&lt;img \x12src=x onerror="javascript:alert(168)"&gt;</t>
         </is>
       </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -2719,6 +6054,9 @@
           <t xml:space="preserve">&lt;img\x47src=x onerror="javascript:alert(169)"&gt;</t>
         </is>
       </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -2726,6 +6064,9 @@
           <t xml:space="preserve">&lt;img\x10src=x onerror="javascript:alert(170)"&gt;</t>
         </is>
       </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -2733,6 +6074,9 @@
           <t xml:space="preserve">&lt;img\x13src=x onerror="javascript:alert(171)"&gt;</t>
         </is>
       </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -2740,6 +6084,9 @@
           <t xml:space="preserve">&lt;img\x32src=x onerror="javascript:alert(172)"&gt;</t>
         </is>
       </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -2747,6 +6094,9 @@
           <t xml:space="preserve">&lt;img\x47src=x onerror="javascript:alert(173)"&gt;</t>
         </is>
       </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -2754,6 +6104,9 @@
           <t xml:space="preserve">&lt;img\x11src=x onerror="javascript:alert(174)"&gt;</t>
         </is>
       </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -2761,6 +6114,9 @@
           <t xml:space="preserve">&lt;img \x47src=x onerror="javascript:alert(175)"&gt;</t>
         </is>
       </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -2768,6 +6124,9 @@
           <t xml:space="preserve">&lt;img \x34src=x onerror="javascript:alert(176)"&gt;</t>
         </is>
       </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -2775,6 +6134,9 @@
           <t xml:space="preserve">&lt;img \x39src=x onerror="javascript:alert(177)"&gt;</t>
         </is>
       </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -2782,6 +6144,9 @@
           <t xml:space="preserve">&lt;img \x00src=x onerror="javascript:alert(178)"&gt;</t>
         </is>
       </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -2789,6 +6154,9 @@
           <t xml:space="preserve">&lt;img src\x09=x onerror="javascript:alert(179)"&gt;</t>
         </is>
       </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -2796,6 +6164,9 @@
           <t xml:space="preserve">&lt;img src\x10=x onerror="javascript:alert(180)"&gt;</t>
         </is>
       </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -2803,6 +6174,9 @@
           <t xml:space="preserve">&lt;img src\x13=x onerror="javascript:alert(181)"&gt;</t>
         </is>
       </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -2810,6 +6184,9 @@
           <t xml:space="preserve">&lt;img src\x32=x onerror="javascript:alert(182)"&gt;</t>
         </is>
       </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -2817,6 +6194,9 @@
           <t xml:space="preserve">&lt;img src\x12=x onerror="javascript:alert(183)"&gt;</t>
         </is>
       </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -2824,6 +6204,9 @@
           <t xml:space="preserve">&lt;img src\x11=x onerror="javascript:alert(184)"&gt;</t>
         </is>
       </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -2831,6 +6214,9 @@
           <t xml:space="preserve">&lt;img src\x00=x onerror="javascript:alert(185)"&gt;</t>
         </is>
       </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -2838,6 +6224,9 @@
           <t xml:space="preserve">&lt;img src\x47=x onerror="javascript:alert(186)"&gt;</t>
         </is>
       </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -2845,6 +6234,9 @@
           <t xml:space="preserve">&lt;img src=x\x09onerror="javascript:alert(187)"&gt;</t>
         </is>
       </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -2852,6 +6244,9 @@
           <t xml:space="preserve">&lt;img src=x\x10onerror="javascript:alert(188)"&gt;</t>
         </is>
       </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -2859,6 +6254,9 @@
           <t xml:space="preserve">&lt;img src=x\x11onerror="javascript:alert(189)"&gt;</t>
         </is>
       </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -2866,6 +6264,9 @@
           <t xml:space="preserve">&lt;img src=x\x12onerror="javascript:alert(190)"&gt;</t>
         </is>
       </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -2873,6 +6274,9 @@
           <t xml:space="preserve">&lt;img src=x\x13onerror="javascript:alert(191)"&gt;</t>
         </is>
       </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -2880,6 +6284,9 @@
           <t xml:space="preserve">&lt;img[a][b][c]src[d]=x[e]onerror=[f]"alert(192)"&gt;</t>
         </is>
       </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -2887,6 +6294,9 @@
           <t xml:space="preserve">&lt;img src=x onerror=\x09"javascript:alert(193)"&gt;</t>
         </is>
       </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -2894,6 +6304,9 @@
           <t xml:space="preserve">&lt;img src=x onerror=\x10"javascript:alert(194)"&gt;</t>
         </is>
       </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -2901,6 +6314,9 @@
           <t xml:space="preserve">&lt;img src=x onerror=\x11"javascript:alert(195)"&gt;</t>
         </is>
       </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -2908,6 +6324,9 @@
           <t xml:space="preserve">&lt;img src=x onerror=\x12"javascript:alert(196)"&gt;</t>
         </is>
       </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -2915,6 +6334,9 @@
           <t xml:space="preserve">&lt;img src=x onerror=\x32"javascript:alert(197)"&gt;</t>
         </is>
       </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -2922,6 +6344,9 @@
           <t xml:space="preserve">&lt;img src=x onerror=\x00"javascript:alert(198)"&gt;</t>
         </is>
       </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -2929,6 +6354,20 @@
           <t xml:space="preserve">&lt;a href=java&amp;#1&amp;#2&amp;#3&amp;#4&amp;#5&amp;#6&amp;#7&amp;#8&amp;#11&amp;#12script:javascript:alert(199)&gt;XXX&lt;/a&gt;</t>
         </is>
       </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+              <color rgb="FF0563C1"/>
+            </rPr>
+            <t xml:space="preserve">XXX</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (javascript:javascript:alert(199))</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -2936,6 +6375,9 @@
           <t xml:space="preserve">&lt;img src="x` `&lt;script&gt;javascript:alert(200)&lt;/script&gt;"` `&gt;</t>
         </is>
       </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -2943,6 +6385,9 @@
           <t xml:space="preserve">&lt;img src onerror /" '"= alt=javascript:alert(201)//"&gt;</t>
         </is>
       </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -2950,6 +6395,13 @@
           <t xml:space="preserve">&lt;title onpropertychange=javascript:alert(202)&gt;&lt;/title&gt;&lt;title title=&gt;</t>
         </is>
       </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">&lt;/body&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -2957,6 +6409,16 @@
           <t xml:space="preserve">&lt;a href=http://foo.bar/#x=`y&gt;&lt;/a&gt;&lt;img alt="`&gt;&lt;img src=x:x onerror=javascript:alert(203)&gt;&lt;/a&gt;"&gt;</t>
         </is>
       </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> (http://foo.bar/#x=`y)</t>
+          </r>
+          <r>
+            <t xml:space="preserve">`&gt;&lt;img src=x:x onerror=javascript:alert(203)&gt;&lt;/a&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -2964,6 +6426,9 @@
           <t xml:space="preserve">&lt;!--[if]&gt;&lt;script&gt;javascript:alert(204)&lt;/script --&gt;</t>
         </is>
       </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -2971,6 +6436,9 @@
           <t xml:space="preserve">&lt;!--[if&lt;img src=x onerror=javascript:alert(205)//]&gt; --&gt;</t>
         </is>
       </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -2978,6 +6446,9 @@
           <t xml:space="preserve">&lt;script src="/\%(jscript)s"&gt;&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -2985,6 +6456,9 @@
           <t xml:space="preserve">&lt;script src="\\%(jscript)s"&gt;&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -2992,6 +6466,16 @@
           <t xml:space="preserve">&lt;IMG """&gt;&lt;SCRIPT&gt;alert("206")&lt;/SCRIPT&gt;"&gt;</t>
         </is>
       </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">alert("206")</t>
+          </r>
+          <r>
+            <t xml:space="preserve">"&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -2999,6 +6483,9 @@
           <t xml:space="preserve">&lt;IMG SRC=javascript:alert(String.fromCharCode(50,48,55))&gt;</t>
         </is>
       </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -3006,6 +6493,9 @@
           <t xml:space="preserve">&lt;IMG SRC=# onmouseover="alert('208')"&gt;</t>
         </is>
       </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -3013,6 +6503,9 @@
           <t xml:space="preserve">&lt;IMG SRC= onmouseover="alert('209')"&gt;</t>
         </is>
       </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -3020,6 +6513,9 @@
           <t xml:space="preserve">&lt;IMG onmouseover="alert('210')"&gt;</t>
         </is>
       </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -3027,6 +6523,9 @@
           <t xml:space="preserve">&lt;IMG SRC=&amp;#106;&amp;#97;&amp;#118;&amp;#97;&amp;#115;&amp;#99;&amp;#114;&amp;#105;&amp;#112;&amp;#116;&amp;#58;&amp;#97;&amp;#108;&amp;#101;&amp;#114;&amp;#116;&amp;#40;&amp;#39;&amp;#50;&amp;#49;&amp;#49;&amp;#39;&amp;#41;&gt;</t>
         </is>
       </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -3034,6 +6533,9 @@
           <t xml:space="preserve">&lt;IMG SRC=&amp;#0000106&amp;#0000097&amp;#0000118&amp;#0000097&amp;#0000115&amp;#0000099&amp;#0000114&amp;#0000105&amp;#0000112&amp;#0000116&amp;#0000058&amp;#0000097&amp;#0000108&amp;#0000101&amp;#0000114&amp;#0000116&amp;#0000040&amp;#0000039&amp;#0000050&amp;#0000049&amp;#0000050&amp;#0000039&amp;#0000041&gt;</t>
         </is>
       </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -3041,6 +6543,9 @@
           <t xml:space="preserve">&lt;IMG SRC=&amp;#x6A&amp;#x61&amp;#x76&amp;#x61&amp;#x73&amp;#x63&amp;#x72&amp;#x69&amp;#x70&amp;#x74&amp;#x3A&amp;#x61&amp;#x6C&amp;#x65&amp;#x72&amp;#x74&amp;#x28&amp;#x27&amp;#x32&amp;#x31&amp;#x33&amp;#x27&amp;#x29&gt;</t>
         </is>
       </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -3048,6 +6553,9 @@
           <t xml:space="preserve">&lt;IMG SRC="jav   ascript:alert('214');"&gt;</t>
         </is>
       </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -3055,6 +6563,9 @@
           <t xml:space="preserve">&lt;IMG SRC="jav&amp;#x09;ascript:alert('215');"&gt;</t>
         </is>
       </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -3062,6 +6573,9 @@
           <t xml:space="preserve">&lt;IMG SRC="jav&amp;#x0A;ascript:alert('216');"&gt;</t>
         </is>
       </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -3069,6 +6583,9 @@
           <t xml:space="preserve">&lt;IMG SRC="jav&amp;#x0D;ascript:alert('217');"&gt;</t>
         </is>
       </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -3076,6 +6593,16 @@
           <t xml:space="preserve">perl -e 'print "&lt;IMG SRC=java\0script:alert(\"218\")&gt;";' &gt; out</t>
         </is>
       </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">perl -e 'print "</t>
+          </r>
+          <r>
+            <t xml:space="preserve">";' &gt; out</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -3083,6 +6610,9 @@
           <t xml:space="preserve">&lt;IMG SRC=" &amp;#14;  javascript:alert('219');"&gt;</t>
         </is>
       </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -3090,6 +6620,9 @@
           <t xml:space="preserve">&lt;SCRIPT/XSS SRC="http://ha.ckers.org/xss.js"&gt;&lt;/SCRIPT&gt;</t>
         </is>
       </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -3097,6 +6630,9 @@
           <t xml:space="preserve">&lt;BODY onload!#$%&amp;()*~+-_.,:;?@[/|\]^`=alert("220")&gt;</t>
         </is>
       </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -3104,6 +6640,9 @@
           <t xml:space="preserve">&lt;SCRIPT/SRC="http://ha.ckers.org/xss.js"&gt;&lt;/SCRIPT&gt;</t>
         </is>
       </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -3111,6 +6650,16 @@
           <t xml:space="preserve">&lt;&lt;SCRIPT&gt;alert("221");//&lt;&lt;/SCRIPT&gt;</t>
         </is>
       </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">&lt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">alert("221");//&lt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -3118,6 +6667,13 @@
           <t xml:space="preserve">&lt;SCRIPT SRC=http://ha.ckers.org/xss.js?&lt; B &gt;</t>
         </is>
       </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">&lt;/body&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -3125,6 +6681,13 @@
           <t xml:space="preserve">&lt;SCRIPT SRC=//ha.ckers.org/.j&gt;</t>
         </is>
       </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">&lt;/body&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -3132,6 +6695,9 @@
           <t xml:space="preserve">&lt;IMG SRC="javascript:alert('222')"</t>
         </is>
       </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -3139,6 +6705,9 @@
           <t xml:space="preserve">&lt;iframe src=http://ha.ckers.org/scriptlet.html &lt;</t>
         </is>
       </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -3146,6 +6715,13 @@
           <t xml:space="preserve">\";alert('223');//</t>
         </is>
       </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">\";alert('223');//</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -3153,6 +6729,16 @@
           <t xml:space="preserve">&lt;u oncopy=alert()&gt; Copy me&lt;/u&gt;</t>
         </is>
       </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <u/>
+            </rPr>
+            <t xml:space="preserve"> Copy me</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -3160,6 +6746,16 @@
           <t xml:space="preserve">&lt;i onwheel=alert(224)&gt; Scroll over me &lt;/i&gt;</t>
         </is>
       </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <i/>
+            </rPr>
+            <t xml:space="preserve"> Scroll over me </t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -3167,6 +6763,13 @@
           <t xml:space="preserve">&lt;plaintext&gt;</t>
         </is>
       </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">&lt;/body&gt;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -3174,6 +6777,13 @@
           <t xml:space="preserve">http://a/%%30%30</t>
         </is>
       </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">http://a/%%30%30</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -3181,6 +6791,13 @@
           <t xml:space="preserve">&lt;/textarea&gt;&lt;script&gt;alert(225)&lt;/script&gt;</t>
         </is>
       </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">alert(225)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -3188,6 +6805,13 @@
           <t xml:space="preserve">1;DROP TABLE users</t>
         </is>
       </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1;DROP TABLE users</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -3195,6 +6819,13 @@
           <t xml:space="preserve">1'; DROP TABLE users-- 1</t>
         </is>
       </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1'; DROP TABLE users-- 1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -3202,6 +6833,13 @@
           <t xml:space="preserve">' OR 1=1 -- 1</t>
         </is>
       </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">' OR 1=1 -- 1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -3209,6 +6847,13 @@
           <t xml:space="preserve">' OR '1'='1</t>
         </is>
       </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">' OR '1'='1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -3216,6 +6861,13 @@
           <t xml:space="preserve">'; EXEC sp_MSForEachTable 'DROP TABLE ?'; --</t>
         </is>
       </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">'; EXEC sp_MSForEachTable 'DROP TABLE ?'; --</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -3223,6 +6875,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is/>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -3230,6 +6885,13 @@
           <t xml:space="preserve">%</t>
         </is>
       </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">%</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -3237,6 +6899,13 @@
           <t xml:space="preserve">_</t>
         </is>
       </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">_</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -3244,6 +6913,13 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">-</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -3251,6 +6927,13 @@
           <t xml:space="preserve">--</t>
         </is>
       </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">--</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -3258,6 +6941,13 @@
           <t xml:space="preserve">--version</t>
         </is>
       </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">--version</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -3265,6 +6955,13 @@
           <t xml:space="preserve">--help</t>
         </is>
       </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">--help</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -3272,6 +6969,13 @@
           <t xml:space="preserve">$USER</t>
         </is>
       </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">$USER</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -3279,6 +6983,13 @@
           <t xml:space="preserve">/dev/null; touch /tmp/blns.fail ; echo</t>
         </is>
       </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">/dev/null; touch /tmp/blns.fail ; echo</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -3286,6 +6997,13 @@
           <t xml:space="preserve">`touch /tmp/blns.fail`</t>
         </is>
       </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">`touch /tmp/blns.fail`</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -3293,6 +7011,13 @@
           <t xml:space="preserve">$(touch /tmp/blns.fail)</t>
         </is>
       </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">$(touch /tmp/blns.fail)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
@@ -3300,6 +7025,13 @@
           <t xml:space="preserve">@{[system "touch /tmp/blns.fail"]}</t>
         </is>
       </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">@{[system "touch /tmp/blns.fail"]}</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -3307,6 +7039,13 @@
           <t xml:space="preserve">eval("puts 'hello world'")</t>
         </is>
       </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">eval("puts 'hello world'")</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -3314,6 +7053,13 @@
           <t xml:space="preserve">System("ls -al /")</t>
         </is>
       </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">System("ls -al /")</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -3321,6 +7067,13 @@
           <t xml:space="preserve">`ls -al /`</t>
         </is>
       </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">`ls -al /`</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -3328,6 +7081,13 @@
           <t xml:space="preserve">Kernel.exec("ls -al /")</t>
         </is>
       </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Kernel.exec("ls -al /")</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
@@ -3335,6 +7095,13 @@
           <t xml:space="preserve">Kernel.exit(1)</t>
         </is>
       </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Kernel.exit(1)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -3342,6 +7109,13 @@
           <t xml:space="preserve">%x('ls -al /')</t>
         </is>
       </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">%x('ls -al /')</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -3349,6 +7123,16 @@
           <t xml:space="preserve">&lt;?xml version="1.0" encoding="ISO-8859-1"?&gt;&lt;!DOCTYPE foo [ &lt;!ELEMENT foo ANY &gt;&lt;!ENTITY xxe SYSTEM "file:///etc/passwd" &gt;]&gt;&lt;foo&gt;&amp;xxe;&lt;/foo&gt;</t>
         </is>
       </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">]&gt;</t>
+          </r>
+          <r>
+            <t xml:space="preserve">&amp;xxe;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -3356,6 +7140,13 @@
           <t xml:space="preserve">$HOME</t>
         </is>
       </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">$HOME</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -3363,6 +7154,13 @@
           <t xml:space="preserve">$ENV{'HOME'}</t>
         </is>
       </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">$ENV{'HOME'}</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -3370,6 +7168,13 @@
           <t xml:space="preserve">%d</t>
         </is>
       </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">%d</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
@@ -3377,6 +7182,13 @@
           <t xml:space="preserve">%s%s%s%s%s</t>
         </is>
       </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">%s%s%s%s%s</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -3384,6 +7196,13 @@
           <t xml:space="preserve">{0}</t>
         </is>
       </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">{0}</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
@@ -3391,6 +7210,13 @@
           <t xml:space="preserve">%*.*s</t>
         </is>
       </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">%*.*s</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -3398,6 +7224,13 @@
           <t xml:space="preserve">%@</t>
         </is>
       </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">%@</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -3405,6 +7238,13 @@
           <t xml:space="preserve">%n</t>
         </is>
       </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">%n</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -3412,6 +7252,13 @@
           <t xml:space="preserve">File:///</t>
         </is>
       </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">File:///</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -3419,6 +7266,13 @@
           <t xml:space="preserve">../../../../../../../../../../../etc/passwd%00</t>
         </is>
       </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">../../../../../../../../../../../etc/passwd%00</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -3426,6 +7280,13 @@
           <t xml:space="preserve">../../../../../../../../../../../etc/hosts</t>
         </is>
       </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">../../../../../../../../../../../etc/hosts</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
@@ -3433,6 +7294,13 @@
           <t xml:space="preserve">() { 0; }; touch /tmp/blns.shellshock1.fail;</t>
         </is>
       </c>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">() { 0; }; touch /tmp/blns.shellshock1.fail;</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -3440,6 +7308,13 @@
           <t xml:space="preserve">() { _; } &gt;_[$($())] { touch /tmp/blns.shellshock2.fail; }</t>
         </is>
       </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">() { _; } &gt;_[$($())] { touch /tmp/blns.shellshock2.fail; }</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -3447,6 +7322,13 @@
           <t xml:space="preserve">&lt;&lt;&lt; %s(un='%s') = %u</t>
         </is>
       </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">&lt;&lt;&lt; %s(un='%s') = %u</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -3454,6 +7336,13 @@
           <t xml:space="preserve">+++ATH0</t>
         </is>
       </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">+++ATH0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
@@ -3461,6 +7350,13 @@
           <t xml:space="preserve">CON</t>
         </is>
       </c>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CON</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -3468,6 +7364,13 @@
           <t xml:space="preserve">PRN</t>
         </is>
       </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">PRN</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
@@ -3475,6 +7378,13 @@
           <t xml:space="preserve">AUX</t>
         </is>
       </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">AUX</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -3482,6 +7392,13 @@
           <t xml:space="preserve">CLOCK$</t>
         </is>
       </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLOCK$</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -3489,6 +7406,13 @@
           <t xml:space="preserve">NUL</t>
         </is>
       </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">NUL</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -3496,6 +7420,13 @@
           <t xml:space="preserve">A:</t>
         </is>
       </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">A:</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -3503,6 +7434,13 @@
           <t xml:space="preserve">ZZ:</t>
         </is>
       </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ZZ:</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -3510,6 +7448,13 @@
           <t xml:space="preserve">COM1</t>
         </is>
       </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">COM1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
@@ -3517,6 +7462,13 @@
           <t xml:space="preserve">LPT1</t>
         </is>
       </c>
+      <c r="B495" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">LPT1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -3524,6 +7476,13 @@
           <t xml:space="preserve">LPT2</t>
         </is>
       </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">LPT2</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
@@ -3531,6 +7490,13 @@
           <t xml:space="preserve">LPT3</t>
         </is>
       </c>
+      <c r="B497" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">LPT3</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -3538,6 +7504,13 @@
           <t xml:space="preserve">COM2</t>
         </is>
       </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">COM2</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
@@ -3545,6 +7518,13 @@
           <t xml:space="preserve">COM3</t>
         </is>
       </c>
+      <c r="B499" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">COM3</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
@@ -3552,6 +7532,13 @@
           <t xml:space="preserve">COM4</t>
         </is>
       </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">COM4</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
@@ -3559,6 +7546,13 @@
           <t xml:space="preserve">DCC SEND STARTKEYLOGGER 0 0 0</t>
         </is>
       </c>
+      <c r="B501" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DCC SEND STARTKEYLOGGER 0 0 0</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -3566,6 +7560,13 @@
           <t xml:space="preserve">Scunthorpe General Hospital</t>
         </is>
       </c>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Scunthorpe General Hospital</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
@@ -3573,6 +7574,13 @@
           <t xml:space="preserve">Penistone Community Church</t>
         </is>
       </c>
+      <c r="B503" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Penistone Community Church</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -3580,6 +7588,13 @@
           <t xml:space="preserve">Lightwater Country Park</t>
         </is>
       </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Lightwater Country Park</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
@@ -3587,6 +7602,13 @@
           <t xml:space="preserve">Jimmy Clitheroe</t>
         </is>
       </c>
+      <c r="B505" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Jimmy Clitheroe</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
@@ -3594,6 +7616,13 @@
           <t xml:space="preserve">Horniman Museum</t>
         </is>
       </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Horniman Museum</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
@@ -3601,6 +7630,13 @@
           <t xml:space="preserve">shitake mushrooms</t>
         </is>
       </c>
+      <c r="B507" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">shitake mushrooms</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -3608,6 +7644,13 @@
           <t xml:space="preserve">RomansInSussex.co.uk</t>
         </is>
       </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">RomansInSussex.co.uk</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
@@ -3615,6 +7658,13 @@
           <t xml:space="preserve">http://www.cum.qc.ca/</t>
         </is>
       </c>
+      <c r="B509" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">http://www.cum.qc.ca/</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
@@ -3622,6 +7672,13 @@
           <t xml:space="preserve">Craig Cockburn, Software Specialist</t>
         </is>
       </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Craig Cockburn, Software Specialist</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
@@ -3629,6 +7686,13 @@
           <t xml:space="preserve">Linda Callahan</t>
         </is>
       </c>
+      <c r="B511" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Linda Callahan</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
@@ -3636,6 +7700,13 @@
           <t xml:space="preserve">Dr. Herman I. Libshitz</t>
         </is>
       </c>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Dr. Herman I. Libshitz</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
@@ -3643,6 +7714,13 @@
           <t xml:space="preserve">magna cum laude</t>
         </is>
       </c>
+      <c r="B513" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">magna cum laude</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
@@ -3650,6 +7728,13 @@
           <t xml:space="preserve">Super Bowl XXX</t>
         </is>
       </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Super Bowl XXX</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
@@ -3657,6 +7742,13 @@
           <t xml:space="preserve">medieval erection of parapets</t>
         </is>
       </c>
+      <c r="B515" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">medieval erection of parapets</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
@@ -3664,6 +7756,13 @@
           <t xml:space="preserve">evaluate</t>
         </is>
       </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">evaluate</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
@@ -3671,6 +7770,13 @@
           <t xml:space="preserve">mocha</t>
         </is>
       </c>
+      <c r="B517" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">mocha</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
@@ -3678,6 +7784,13 @@
           <t xml:space="preserve">expression</t>
         </is>
       </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">expression</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
@@ -3685,6 +7798,13 @@
           <t xml:space="preserve">Arsenal canal</t>
         </is>
       </c>
+      <c r="B519" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Arsenal canal</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
@@ -3692,6 +7812,13 @@
           <t xml:space="preserve">classic</t>
         </is>
       </c>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">classic</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
@@ -3699,6 +7826,13 @@
           <t xml:space="preserve">Tyson Gay</t>
         </is>
       </c>
+      <c r="B521" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Tyson Gay</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
@@ -3706,6 +7840,13 @@
           <t xml:space="preserve">Dick Van Dyke</t>
         </is>
       </c>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Dick Van Dyke</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
@@ -3713,6 +7854,13 @@
           <t xml:space="preserve">basement</t>
         </is>
       </c>
+      <c r="B523" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">basement</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
@@ -3720,6 +7868,13 @@
           <t xml:space="preserve">If you're reading this, you've been in a coma for almost 20 years now. We're trying a new technique. We don't know where this message will end up in your dream, but we hope it works. Please wake up, we miss you.</t>
         </is>
       </c>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">If you're reading this, you've been in a coma for almost 20 years now. We're trying a new technique. We don't know where this message will end up in your dream, but we hope it works. Please wake up, we miss you.</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
@@ -3727,6 +7882,13 @@
           <t xml:space="preserve">Roses are [0;31mred[0m, violets are [0;34mblue. Hope you enjoy terminal hue</t>
         </is>
       </c>
+      <c r="B525" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Roses are [0;31mred[0m, violets are [0;34mblue. Hope you enjoy terminal hue</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
@@ -3734,6 +7896,13 @@
           <t xml:space="preserve">But now...[20Cfor my greatest trick...[8m</t>
         </is>
       </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">But now...[20Cfor my greatest trick...[8m</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
@@ -3741,6 +7910,13 @@
           <t xml:space="preserve">The quick brown fox... [Beeeep]</t>
         </is>
       </c>
+      <c r="B527" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">The quick brown fox... [Beeeep]</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
@@ -3748,6 +7924,13 @@
           <t xml:space="preserve">Powerلُلُصّبُلُلصّبُررً ॣ ॣh ॣ ॣ冗</t>
         </is>
       </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Powerلُلُصّبُلُلصّبُررً ॣ ॣh ॣ ॣ冗</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
@@ -3755,6 +7938,13 @@
           <t xml:space="preserve">🏳0🌈️</t>
         </is>
       </c>
+      <c r="B529" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">🏳0🌈️</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
@@ -3762,6 +7952,13 @@
           <t xml:space="preserve">జ్ఞ‌ా</t>
         </is>
       </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">జ్ఞ‌ా</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
@@ -3769,6 +7966,13 @@
           <t xml:space="preserve">گچپژ</t>
         </is>
       </c>
+      <c r="B531" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">گچپژ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
@@ -3776,6 +7980,13 @@
           <t xml:space="preserve">{% print 'x' * 64 * 1024**3 %}</t>
         </is>
       </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">{% print 'x' * 64 * 1024**3 %}</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
@@ -3783,6 +7994,13 @@
           <t xml:space="preserve">{{ "".__class__.__mro__[2].__subclasses__()[40]("/etc/passwd").read() }}</t>
         </is>
       </c>
+      <c r="B533" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">{{ "".__class__.__mro__[2].__subclasses__()[40]("/etc/passwd").read() }}</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
@@ -3790,6 +8008,13 @@
           <t xml:space="preserve">En dash –</t>
         </is>
       </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">En dash –</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
@@ -3797,6 +8022,13 @@
           <t xml:space="preserve">Em dash —</t>
         </is>
       </c>
+      <c r="B535" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Em dash —</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
@@ -3804,6 +8036,13 @@
           <t xml:space="preserve">Horizontal bar ―</t>
         </is>
       </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Horizontal bar ―</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
@@ -3811,6 +8050,13 @@
           <t xml:space="preserve">Figure dash ‒</t>
         </is>
       </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Figure dash ‒</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
@@ -3818,6 +8064,13 @@
           <t xml:space="preserve">Swung dash ⁓</t>
         </is>
       </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Swung dash ⁓</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
@@ -3825,6 +8078,13 @@
           <t xml:space="preserve">Single opening quote ‘</t>
         </is>
       </c>
+      <c r="B539" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Single opening quote ‘</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
@@ -3832,6 +8092,13 @@
           <t xml:space="preserve">Single closing quote ’</t>
         </is>
       </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Single closing quote ’</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
@@ -3839,6 +8106,13 @@
           <t xml:space="preserve">Double opening quote “</t>
         </is>
       </c>
+      <c r="B541" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Double opening quote “</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
@@ -3846,6 +8120,13 @@
           <t xml:space="preserve">Double closing quote ”</t>
         </is>
       </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Double closing quote ”</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
@@ -3853,6 +8134,13 @@
           <t xml:space="preserve">Copyright ©</t>
         </is>
       </c>
+      <c r="B543" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Copyright ©</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
@@ -3860,6 +8148,13 @@
           <t xml:space="preserve">Registered ®</t>
         </is>
       </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Registered ®</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
@@ -3867,6 +8162,13 @@
           <t xml:space="preserve">Trademark ™</t>
         </is>
       </c>
+      <c r="B545" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Trademark ™</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
@@ -3874,6 +8176,13 @@
           <t xml:space="preserve">Section §</t>
         </is>
       </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Section §</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
@@ -3881,6 +8190,13 @@
           <t xml:space="preserve">Paragraph ¶</t>
         </is>
       </c>
+      <c r="B547" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Paragraph ¶</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
@@ -3888,6 +8204,13 @@
           <t xml:space="preserve">Ellipsis …</t>
         </is>
       </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Ellipsis …</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
@@ -3895,6 +8218,13 @@
           <t xml:space="preserve">Optional hyphen ¬</t>
         </is>
       </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Optional hyphen ¬</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
@@ -3902,6 +8232,13 @@
           <t xml:space="preserve">Non-breaking hyphen ߛ</t>
         </is>
       </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Non-breaking hyphen ߛ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
@@ -3909,6 +8246,13 @@
           <t xml:space="preserve">Em space ߓ</t>
         </is>
       </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Em space ߓ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
@@ -3916,6 +8260,13 @@
           <t xml:space="preserve">En space ߒ</t>
         </is>
       </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">En space ߒ</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
@@ -3923,8 +8274,15 @@
           <t xml:space="preserve">Quarter space ߕ</t>
         </is>
       </c>
+      <c r="B553" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Quarter space ߕ</t>
+          </r>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A553"/>
+  <autoFilter ref="A1:B553"/>
 </worksheet>
 </file>
--- a/src/Excelsior.Tests/NaughtyStringsTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/NaughtyStringsTests.Test.verified.xlsx
@@ -1445,7 +1445,11 @@
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
-        <is/>
+        <is>
+          <r>
+            <t xml:space="preserve"/>
+          </r>
+        </is>
       </c>
     </row>
     <row r="101">

--- a/src/Excelsior.Tests/NaughtyStringsTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/NaughtyStringsTests.Test.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -8289,4 +8289,13 @@
   </sheetData>
   <autoFilter ref="A1:B553"/>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Sheet1">
+    <column index="1" property="Value"/>
+    <column index="2" property="Html"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/Excelsior.Tests/NaughtyStringsTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/NaughtyStringsTests.Test.verified.xlsx
@@ -2997,11 +2997,7 @@
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">alert(0)</t>
-          </r>
-        </is>
+        <is/>
       </c>
     </row>
     <row r="213">
@@ -3049,9 +3045,6 @@
           <r>
             <t xml:space="preserve">"&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">alert(4)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -3066,9 +3059,6 @@
           <r>
             <t xml:space="preserve">'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">alert(5)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -3083,9 +3073,6 @@
           <r>
             <t xml:space="preserve">&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">alert(6)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -3096,11 +3083,7 @@
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">alert(7)</t>
-          </r>
-        </is>
+        <is/>
       </c>
     </row>
     <row r="220">
@@ -3198,9 +3181,6 @@
           <r>
             <t xml:space="preserve">--&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">alert(14)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -3285,9 +3265,6 @@
           <r>
             <t xml:space="preserve">"&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">alert(20);</t>
-          </r>
         </is>
       </c>
     </row>
@@ -3302,9 +3279,6 @@
           <r>
             <t xml:space="preserve">'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">alert(21);</t>
-          </r>
         </is>
       </c>
     </row>
@@ -3318,9 +3292,6 @@
         <is>
           <r>
             <t xml:space="preserve">&gt;</t>
-          </r>
-          <r>
-            <t xml:space="preserve">alert(22);</t>
           </r>
         </is>
       </c>
@@ -5394,9 +5365,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\x3Bjavascript:alert(128)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5411,9 +5379,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\x0Djavascript:alert(129)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5428,9 +5393,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xEF\xBB\xBFjavascript:alert(130)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5445,9 +5407,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE2\x80\x81javascript:alert(131)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5462,9 +5421,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE2\x80\x84javascript:alert(132)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5479,9 +5435,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE3\x80\x80javascript:alert(133)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5496,9 +5449,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\x09javascript:alert(134)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5513,9 +5463,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE2\x80\x89javascript:alert(135)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5530,9 +5477,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE2\x80\x85javascript:alert(136)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5547,9 +5491,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE2\x80\x88javascript:alert(137)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5564,9 +5505,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\x00javascript:alert(138)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5581,9 +5519,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE2\x80\xA8javascript:alert(139)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5598,9 +5533,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE2\x80\x8Ajavascript:alert(140)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5615,9 +5547,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE1\x9A\x80javascript:alert(141)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5632,9 +5561,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\x0Cjavascript:alert(142)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5649,9 +5575,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\x2Bjavascript:alert(143)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5666,9 +5589,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xF0\x90\x96\x9Ajavascript:alert(144)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5683,9 +5603,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">-javascript:alert(145)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5700,9 +5617,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\x0Ajavascript:alert(146)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5717,9 +5631,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE2\x80\xAFjavascript:alert(147)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5734,9 +5645,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\x7Ejavascript:alert(148)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5751,9 +5659,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE2\x80\x87javascript:alert(149)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5768,9 +5673,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE2\x81\x9Fjavascript:alert(150)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5785,9 +5687,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE2\x80\xA9javascript:alert(151)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5802,9 +5701,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xC2\x85javascript:alert(152)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5819,9 +5715,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xEF\xBF\xAEjavascript:alert(153)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5836,9 +5729,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE2\x80\x83javascript:alert(154)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5853,9 +5743,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE2\x80\x8Bjavascript:alert(155)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5870,9 +5757,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xEF\xBF\xBEjavascript:alert(156)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5887,9 +5771,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE2\x80\x80javascript:alert(157)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5904,9 +5785,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\x21javascript:alert(158)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5921,9 +5799,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE2\x80\x82javascript:alert(159)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5938,9 +5813,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE2\x80\x86javascript:alert(160)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5955,9 +5827,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\xE1\xA0\x8Ejavascript:alert(161)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5972,9 +5841,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\x0Bjavascript:alert(162)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -5989,9 +5855,6 @@
           <r>
             <t xml:space="preserve">"`'&gt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">\x20javascript:alert(163)</t>
-          </r>
         </is>
       </c>
     </row>
@@ -6005,9 +5868,6 @@
         <is>
           <r>
             <t xml:space="preserve">"`'&gt;</t>
-          </r>
-          <r>
-            <t xml:space="preserve">\xC2\xA0javascript:alert(164)</t>
           </r>
         </is>
       </c>
@@ -6400,11 +6260,7 @@
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">&lt;/body&gt;</t>
-          </r>
-        </is>
+        <is/>
       </c>
     </row>
     <row r="415">
@@ -6473,9 +6329,6 @@
       <c r="B420" s="2" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">alert("206")</t>
-          </r>
-          <r>
             <t xml:space="preserve">"&gt;</t>
           </r>
         </is>
@@ -6659,9 +6512,6 @@
           <r>
             <t xml:space="preserve">&lt;</t>
           </r>
-          <r>
-            <t xml:space="preserve">alert("221");//&lt;</t>
-          </r>
         </is>
       </c>
     </row>
@@ -6672,11 +6522,7 @@
         </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">&lt;/body&gt;</t>
-          </r>
-        </is>
+        <is/>
       </c>
     </row>
     <row r="439">
@@ -6686,11 +6532,7 @@
         </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">&lt;/body&gt;</t>
-          </r>
-        </is>
+        <is/>
       </c>
     </row>
     <row r="440">
@@ -6796,11 +6638,7 @@
         </is>
       </c>
       <c r="B447" s="2" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">alert(225)</t>
-          </r>
-        </is>
+        <is/>
       </c>
     </row>
     <row r="448">
